--- a/AAII_Financials/Quarterly/BVS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BVS_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Quarterly/BVS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BVS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="92">
   <si>
     <t>BVS</t>
   </si>
@@ -656,303 +656,328 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="24" max="24" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45108</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45017</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44835</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44744</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44653</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44471</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44380</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44289</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44100</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44009</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43918</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43645</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>42735</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>42462</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>42369</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>129500</v>
+      </c>
+      <c r="E8" s="3">
+        <v>135400</v>
+      </c>
+      <c r="F8" s="3">
         <v>120800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>137100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>119100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>125800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>128700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>140300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>117300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>130400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>108900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>109800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>81800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>98600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>85900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>136700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>78600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>97600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>160300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>274500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>65400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>71200</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>41100</v>
+      </c>
+      <c r="E9" s="3">
+        <v>49100</v>
+      </c>
+      <c r="F9" s="3">
         <v>41900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>47900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>45100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>51600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>44100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>43700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>41600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>42600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>29800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>33500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>22200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>25100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>23400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>39100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>21400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>24100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>45100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>80400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>19200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>20200</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>88400</v>
+      </c>
+      <c r="E10" s="3">
+        <v>86300</v>
+      </c>
+      <c r="F10" s="3">
         <v>78900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>89200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>74000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>74200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>84600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>96600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>75700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>87800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>79100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>76300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>59600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>73500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>62500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>97600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>57200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>73500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>115200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>194100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>46200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>51000</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -976,73 +1001,81 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E12" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F12" s="3">
         <v>3000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>3400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>3800</v>
       </c>
-      <c r="G12" s="3">
-        <v>6800</v>
-      </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
+        <v>5900</v>
+      </c>
+      <c r="J12" s="3">
         <v>4600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>6400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>6900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>7100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>6200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>4800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>2900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>3600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>4700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>2100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>3100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>5100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>7900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>3700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1106,138 +1139,156 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F14" s="3">
         <v>1400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>1600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>78900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>4600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>314500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>1000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>3900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>5700</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q14" s="3">
         <v>900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>3500</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="U14" s="3">
         <v>3300</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>8800</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>200</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E15" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F15" s="3">
         <v>2300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>2300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>2100</v>
       </c>
-      <c r="G15" s="3">
-        <v>7800</v>
-      </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J15" s="3">
         <v>2300</v>
-      </c>
-      <c r="I15" s="3">
-        <v>2700</v>
-      </c>
-      <c r="J15" s="3">
-        <v>3300</v>
       </c>
       <c r="K15" s="3">
         <v>2700</v>
       </c>
       <c r="L15" s="3">
-        <v>1900</v>
+        <v>3300</v>
       </c>
       <c r="M15" s="3">
-        <v>1900</v>
+        <v>2700</v>
       </c>
       <c r="N15" s="3">
         <v>1900</v>
       </c>
       <c r="O15" s="3">
+        <v>1900</v>
+      </c>
+      <c r="P15" s="3">
+        <v>1900</v>
+      </c>
+      <c r="Q15" s="3">
         <v>2100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>1700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>3600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>1800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>2100</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>3800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>11000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>2800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1258,138 +1309,152 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>124100</v>
+      </c>
+      <c r="E17" s="3">
+        <v>134300</v>
+      </c>
+      <c r="F17" s="3">
         <v>118400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>130300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>211100</v>
       </c>
-      <c r="G17" s="3">
-        <v>151300</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
+        <v>141500</v>
+      </c>
+      <c r="J17" s="3">
         <v>255500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>143600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>138700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>133600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>112100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>115600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>59800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>92700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>75900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>127200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>65700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>86800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>153500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>263600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>67400</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E18" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F18" s="3">
         <v>2400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>6800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-92000</v>
       </c>
-      <c r="G18" s="3">
-        <v>-25500</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
+        <v>-15700</v>
+      </c>
+      <c r="J18" s="3">
         <v>-126800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-3300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-21400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-3200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-3200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-5800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>22000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>5900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>10000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>9500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>12900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>10800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>6900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>10900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-2000</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1413,8 +1478,10 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1422,158 +1489,170 @@
         <v>-500</v>
       </c>
       <c r="E20" s="3">
+        <v>700</v>
+      </c>
+      <c r="F20" s="3">
         <v>-500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="H20" s="3">
         <v>1500</v>
       </c>
-      <c r="G20" s="3">
-        <v>-24200</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="J20" s="3">
         <v>-200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-3200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>1900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-1400</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-3300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>2400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-1900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-2400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-600</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>-700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>500</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E21" s="3">
+        <v>14300</v>
+      </c>
+      <c r="F21" s="3">
         <v>15800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>20800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-74000</v>
       </c>
-      <c r="G21" s="3">
-        <v>-26600</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="J21" s="3">
         <v>-108200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>5900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-7100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>7100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>5400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-1600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>31600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>13000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>17500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>22200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>17800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>17500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>22600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>44000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>7600</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E22" s="3">
+        <v>10300</v>
+      </c>
+      <c r="F22" s="3">
         <v>10100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>10600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>9700</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
+        <v>7400</v>
+      </c>
+      <c r="J22" s="3">
         <v>3600</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>12</v>
+      <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3">
+        <v>0</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>12</v>
@@ -1581,165 +1660,183 @@
       <c r="N22" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="O22" s="3">
+      <c r="O22" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q22" s="3">
         <v>3000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>1900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>3200</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="U22" s="3">
         <v>3900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>9400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>15900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>3900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="F23" s="3">
         <v>-8200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-4400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-100200</v>
       </c>
-      <c r="G23" s="3">
-        <v>-49700</v>
-      </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
+        <v>-32400</v>
+      </c>
+      <c r="J23" s="3">
         <v>-130600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-6500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-19500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-4600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-3200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-9100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>24500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>3100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>8300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>4400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>10500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>6200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-2500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-5700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-5400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-5300</v>
       </c>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>900</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F24" s="3">
         <v>600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>-100</v>
       </c>
-      <c r="G24" s="3">
-        <v>-4800</v>
-      </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="J24" s="3">
         <v>-29500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>1200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>-5100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-2700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>1700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>-100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>-100</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>1100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1803,138 +1900,156 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="F26" s="3">
         <v>-8800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-4700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-100000</v>
       </c>
-      <c r="G26" s="3">
-        <v>-44900</v>
-      </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
+        <v>-21500</v>
+      </c>
+      <c r="J26" s="3">
         <v>-101000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-7700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-14400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-1900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-2300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-10800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>24500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>2300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>8000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>4500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>10500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>5300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-2800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-6700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-6000</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="F27" s="3">
         <v>-7300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-3700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-79700</v>
       </c>
-      <c r="G27" s="3">
-        <v>-31900</v>
-      </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
+        <v>-13200</v>
+      </c>
+      <c r="J27" s="3">
         <v>-72800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-7000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-10900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-1100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-4100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>24900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>3000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>10900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>2700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-5700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-12200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-7100</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1998,8 +2113,14 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2010,61 +2131,67 @@
         <v>0</v>
       </c>
       <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
         <v>-59500</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
+        <v>-18700</v>
+      </c>
+      <c r="J29" s="3">
         <v>-35400</v>
       </c>
-      <c r="I29" s="3">
+      <c r="K29" s="3">
         <v>-300</v>
       </c>
-      <c r="J29" s="3">
+      <c r="L29" s="3">
         <v>-400</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M29" s="3" t="s">
-        <v>12</v>
+      <c r="M29" s="3">
+        <v>0</v>
       </c>
       <c r="N29" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
-      </c>
-      <c r="P29" s="3">
-        <v>0</v>
+      <c r="O29" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>12</v>
+      <c r="R29" s="3">
+        <v>0</v>
       </c>
       <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="U29" s="3">
         <v>-200</v>
       </c>
-      <c r="T29" s="3">
+      <c r="V29" s="3">
         <v>-1600</v>
       </c>
-      <c r="U29" s="3">
+      <c r="W29" s="3">
         <v>-11200</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="W29" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y29" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2128,8 +2255,14 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2193,8 +2326,14 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2202,129 +2341,141 @@
         <v>500</v>
       </c>
       <c r="E32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F32" s="3">
         <v>500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
+        <v>500</v>
+      </c>
+      <c r="H32" s="3">
         <v>-1500</v>
       </c>
-      <c r="G32" s="3">
-        <v>24200</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
+        <v>9400</v>
+      </c>
+      <c r="J32" s="3">
         <v>200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>3200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-1900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>1400</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>3300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-2400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>1900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>2400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>600</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-500</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="F33" s="3">
         <v>-7300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-3700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-139200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-31900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-108200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-7300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-11300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-1100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-4100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>24900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>3000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>10900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>2500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-7400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-23400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-7100</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2388,143 +2539,161 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="F35" s="3">
         <v>-7300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-3700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-139200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-31900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-108200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-7300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-11300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-1100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-4100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>24900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>3000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>10900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>2500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-7400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-23400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-7100</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45108</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45017</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44835</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44744</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44653</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44471</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44380</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44289</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44100</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44009</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43918</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43645</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>42735</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>42462</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>42369</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2548,8 +2717,10 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2573,59 +2744,61 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>25200</v>
+      </c>
+      <c r="E41" s="3">
+        <v>37000</v>
+      </c>
+      <c r="F41" s="3">
         <v>26800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>29400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>47100</v>
       </c>
-      <c r="G41" s="3">
-        <v>31800</v>
-      </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
+        <v>30200</v>
+      </c>
+      <c r="J41" s="3">
         <v>34400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>41000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>27400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>43900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>80900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>136100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>124200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>86800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>72500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>126200</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="S41" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>12</v>
       </c>
@@ -2638,8 +2811,14 @@
       <c r="W41" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y41" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2703,59 +2882,65 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>125500</v>
+      </c>
+      <c r="E43" s="3">
+        <v>123000</v>
+      </c>
+      <c r="F43" s="3">
         <v>112900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>119600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>118500</v>
       </c>
-      <c r="G43" s="3">
-        <v>136900</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
+        <v>136600</v>
+      </c>
+      <c r="J43" s="3">
         <v>132200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>143000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>119300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>125000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>105400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>102000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>89500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>88400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>80900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>67400</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="S43" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>12</v>
       </c>
@@ -2768,59 +2953,65 @@
       <c r="W43" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y43" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>97000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>91300</v>
+      </c>
+      <c r="F44" s="3">
         <v>97600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>96300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>88000</v>
       </c>
-      <c r="G44" s="3">
-        <v>85400</v>
-      </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
+        <v>82900</v>
+      </c>
+      <c r="J44" s="3">
         <v>77000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>69100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>64700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>61700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>36600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>34000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>39800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>29100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>34700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>33800</v>
       </c>
-      <c r="R44" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="S44" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="T44" s="3" t="s">
         <v>12</v>
       </c>
@@ -2833,59 +3024,65 @@
       <c r="W44" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y44" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>18200</v>
+      </c>
+      <c r="E45" s="3">
+        <v>16700</v>
+      </c>
+      <c r="F45" s="3">
         <v>12200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>15300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>55100</v>
       </c>
-      <c r="G45" s="3">
-        <v>18400</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
+        <v>21100</v>
+      </c>
+      <c r="J45" s="3">
         <v>27600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>24100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>34000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>32400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>23200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>17900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>17200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>7500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>5000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>7100</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="S45" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>12</v>
       </c>
@@ -2898,59 +3095,65 @@
       <c r="W45" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y45" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>265900</v>
+      </c>
+      <c r="E46" s="3">
+        <v>268000</v>
+      </c>
+      <c r="F46" s="3">
         <v>249500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>260600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>308700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>272600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>271100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>277200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>245400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>263100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>246100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>290100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>270700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>211800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>193100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>234400</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="S46" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>12</v>
       </c>
@@ -2963,59 +3166,65 @@
       <c r="W46" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y46" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E47" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F47" s="3">
         <v>6900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>6500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>2600</v>
       </c>
-      <c r="G47" s="3">
-        <v>2600</v>
-      </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
+        <v>5300</v>
+      </c>
+      <c r="J47" s="3">
         <v>13000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>78500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>28800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>29300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>29300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>19500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>21200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>19400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>19900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>3400</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="S47" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="T47" s="3" t="s">
         <v>12</v>
       </c>
@@ -3028,59 +3237,65 @@
       <c r="W47" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y47" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>47000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>50000</v>
+      </c>
+      <c r="F48" s="3">
         <v>54000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>57100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>52600</v>
       </c>
-      <c r="G48" s="3">
-        <v>45000</v>
-      </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
+        <v>44100</v>
+      </c>
+      <c r="J48" s="3">
         <v>42900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>43500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>43600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>40200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>27200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>26600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>26100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>21800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>19800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>18900</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="S48" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>12</v>
       </c>
@@ -3093,59 +3308,65 @@
       <c r="W48" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y48" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>478100</v>
+      </c>
+      <c r="E49" s="3">
+        <v>489800</v>
+      </c>
+      <c r="F49" s="3">
         <v>500800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>512700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>523500</v>
       </c>
-      <c r="G49" s="3">
-        <v>1052500</v>
-      </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
+        <v>647300</v>
+      </c>
+      <c r="J49" s="3">
         <v>1071000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>809700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>829300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>842800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>301700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>310000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>324600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>241500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>246500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>252700</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="S49" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="T49" s="3" t="s">
         <v>12</v>
       </c>
@@ -3158,8 +3379,14 @@
       <c r="W49" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y49" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3223,8 +3450,14 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3288,50 +3521,56 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>12</v>
+      <c r="E52" s="3">
+        <v>0</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
+      <c r="G52" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="I52" s="3">
-        <v>0</v>
+        <v>406000</v>
       </c>
       <c r="J52" s="3">
+        <v>0</v>
+      </c>
+      <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3">
         <v>50000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>50500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>50500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>500</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="P52" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>12</v>
       </c>
@@ -3344,17 +3583,23 @@
       <c r="T52" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="U52" s="3">
-        <v>0</v>
-      </c>
-      <c r="V52" s="3">
-        <v>0</v>
+      <c r="U52" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="V52" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="W52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3418,59 +3663,65 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>794200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>810900</v>
+      </c>
+      <c r="F54" s="3">
         <v>811100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>837000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>887400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>1372600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>1398000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>1208800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1197100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>1225900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>654800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>646600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>643100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>494500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>479300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>509400</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="S54" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>12</v>
       </c>
@@ -3483,8 +3734,14 @@
       <c r="W54" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y54" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3508,8 +3765,10 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3533,59 +3792,61 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E57" s="3">
+        <v>23000</v>
+      </c>
+      <c r="F57" s="3">
         <v>17600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>41400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>32800</v>
       </c>
-      <c r="G57" s="3">
-        <v>37500</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
+        <v>36700</v>
+      </c>
+      <c r="J57" s="3">
         <v>19100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>25700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>22500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>16900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>10900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>9900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>10300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>4400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>8800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>13600</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="S57" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>12</v>
       </c>
@@ -3598,40 +3859,46 @@
       <c r="W57" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y57" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>35800</v>
+      </c>
+      <c r="E58" s="3">
+        <v>27800</v>
+      </c>
+      <c r="F58" s="3">
         <v>19600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>11300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>41300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>33100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>31300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>22500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>20300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>18000</v>
-      </c>
-      <c r="L58" s="3">
-        <v>15000</v>
-      </c>
-      <c r="M58" s="3">
-        <v>15000</v>
       </c>
       <c r="N58" s="3">
         <v>15000</v>
@@ -3640,16 +3907,16 @@
         <v>15000</v>
       </c>
       <c r="P58" s="3">
-        <v>16300</v>
+        <v>15000</v>
       </c>
       <c r="Q58" s="3">
         <v>15000</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="S58" s="3" t="s">
-        <v>12</v>
+      <c r="R58" s="3">
+        <v>16300</v>
+      </c>
+      <c r="S58" s="3">
+        <v>15000</v>
       </c>
       <c r="T58" s="3" t="s">
         <v>12</v>
@@ -3663,59 +3930,65 @@
       <c r="W58" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y58" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>118400</v>
+      </c>
+      <c r="E59" s="3">
+        <v>124600</v>
+      </c>
+      <c r="F59" s="3">
         <v>123600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>126400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>121900</v>
       </c>
-      <c r="G59" s="3">
-        <v>233400</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
+        <v>351900</v>
+      </c>
+      <c r="J59" s="3">
         <v>238000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>150600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>128700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>145900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>134800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>133300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>123700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>103200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>86700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>68700</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="S59" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>12</v>
       </c>
@@ -3728,59 +4001,65 @@
       <c r="W59" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y59" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>173300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>175500</v>
+      </c>
+      <c r="F60" s="3">
         <v>160800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>179100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>196100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>304000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>288400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>198900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>171500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>180900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>160700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>158200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>149000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>122600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>111700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>97200</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="S60" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>12</v>
       </c>
@@ -3793,59 +4072,65 @@
       <c r="W60" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y60" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>355400</v>
+      </c>
+      <c r="E61" s="3">
+        <v>367000</v>
+      </c>
+      <c r="F61" s="3">
         <v>375000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>374600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>404300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>385000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>393100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>351400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>348000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>339600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>162400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>166100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>169700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>173400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>177000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>229700</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -3858,59 +4143,65 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>48100</v>
+      </c>
+      <c r="E62" s="3">
+        <v>47300</v>
+      </c>
+      <c r="F62" s="3">
         <v>48800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>49900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>46700</v>
       </c>
-      <c r="G62" s="3">
-        <v>343300</v>
-      </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
+        <v>350700</v>
+      </c>
+      <c r="J62" s="3">
         <v>337400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>138300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>155700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>171600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>101200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>103000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>104000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>54300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>45200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>40700</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="S62" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>12</v>
       </c>
@@ -3923,8 +4214,14 @@
       <c r="W62" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y62" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3988,8 +4285,14 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4053,8 +4356,14 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4118,59 +4427,65 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>623000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>637300</v>
+      </c>
+      <c r="F66" s="3">
         <v>633600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>653800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>698900</v>
       </c>
-      <c r="G66" s="3">
-        <v>1056100</v>
-      </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
+        <v>1047400</v>
+      </c>
+      <c r="J66" s="3">
         <v>1054600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>760800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>747400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>766900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>502300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>505100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>500700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>352200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>336100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>370200</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="S66" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>12</v>
       </c>
@@ -4183,8 +4498,14 @@
       <c r="W66" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y66" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4208,8 +4529,10 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4273,8 +4596,14 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4338,8 +4667,14 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4377,19 +4712,19 @@
         <v>0</v>
       </c>
       <c r="O70" s="3">
-        <v>168000</v>
+        <v>0</v>
       </c>
       <c r="P70" s="3">
-        <v>168000</v>
+        <v>0</v>
       </c>
       <c r="Q70" s="3">
         <v>168000</v>
       </c>
       <c r="R70" s="3">
-        <v>0</v>
+        <v>168000</v>
       </c>
       <c r="S70" s="3">
-        <v>0</v>
+        <v>168000</v>
       </c>
       <c r="T70" s="3">
         <v>0</v>
@@ -4403,8 +4738,14 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4468,59 +4809,65 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-326100</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-321500</v>
+      </c>
+      <c r="F72" s="3">
         <v>-315400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-308100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-304500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-165300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-133400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-25100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-17900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-6600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-6200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-5200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-1000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-140700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-138400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-141500</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="S72" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>12</v>
       </c>
@@ -4533,8 +4880,14 @@
       <c r="W72" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y72" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4598,8 +4951,14 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4663,8 +5022,14 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4728,59 +5093,65 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>171300</v>
+      </c>
+      <c r="E76" s="3">
+        <v>173600</v>
+      </c>
+      <c r="F76" s="3">
         <v>177500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>183200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>188500</v>
       </c>
-      <c r="G76" s="3">
-        <v>316600</v>
-      </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
+        <v>325200</v>
+      </c>
+      <c r="J76" s="3">
         <v>343400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>448000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>449800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>458900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>152500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>141600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>142400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>-25800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>-24800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>-28800</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="S76" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>12</v>
       </c>
@@ -4793,8 +5164,14 @@
       <c r="W76" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y76" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4858,143 +5235,161 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45108</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45017</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44835</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44744</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44653</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44471</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44380</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44289</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44100</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44009</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43918</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43645</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>42735</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>42462</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>42369</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="F81" s="3">
         <v>-7300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-3700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-139200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-31900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-108200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-7300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-11300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-1100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-4100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>24900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>3000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>10900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>2500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-7400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-23400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-7100</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5018,73 +5413,81 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E83" s="3">
+        <v>12500</v>
+      </c>
+      <c r="F83" s="3">
         <v>13800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>14600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>16500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>23200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>18800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>12400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>12500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>11700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>8500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>7500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>7200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>6900</v>
-      </c>
-      <c r="P83" s="3">
-        <v>7300</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>14500</v>
       </c>
       <c r="R83" s="3">
         <v>7300</v>
       </c>
       <c r="S83" s="3">
+        <v>14500</v>
+      </c>
+      <c r="T83" s="3">
         <v>7300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
+        <v>7300</v>
+      </c>
+      <c r="V83" s="3">
         <v>15700</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="X83" s="3">
         <v>9100</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5148,8 +5551,14 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5213,8 +5622,14 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5278,8 +5693,14 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5343,8 +5764,14 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5408,73 +5835,85 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>10400</v>
+      </c>
+      <c r="F89" s="3">
         <v>-8300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>10800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>2500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>5200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>2900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-21000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>13100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>10600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>17300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-18000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>25400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>20800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>25500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>17700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>21000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>8000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>37100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>2200</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5498,73 +5937,81 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F91" s="3">
         <v>-2000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-1400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-3600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-3400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-1600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-2000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-3000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-2800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-1900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-1300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-1400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-1800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-1100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-1300</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="X91" s="3">
         <v>-600</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5628,8 +6075,14 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5693,73 +6146,85 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F94" s="3">
         <v>-2000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>33500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-15100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-3400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-56300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-52000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-4700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-221300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-13200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-2600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-46600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-1700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-17800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-1000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-7300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-7900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-6600</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5783,8 +6248,10 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5848,8 +6315,14 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5913,8 +6386,14 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5978,8 +6457,14 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6043,102 +6528,114 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>8200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-62200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>27400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-5400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>50700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>7700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>9200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>176300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-4300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-6100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>107500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-9900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-57100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>37400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>48800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-11100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-9000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>5500</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E101" s="3">
+        <v>400</v>
+      </c>
+      <c r="F101" s="3">
         <v>-400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>1100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-100</v>
-      </c>
-      <c r="K101" s="3">
-        <v>100</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-200</v>
       </c>
       <c r="M101" s="3">
         <v>100</v>
@@ -6147,95 +6644,107 @@
         <v>-200</v>
       </c>
       <c r="O101" s="3">
+        <v>100</v>
+      </c>
+      <c r="P101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Q101" s="3">
         <v>500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>300</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="X101" s="3">
         <v>200</v>
       </c>
-      <c r="W101" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="E102" s="3">
+        <v>10100</v>
+      </c>
+      <c r="F102" s="3">
         <v>-2600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-17700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>15300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-2500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-6600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-41700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-16600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-31700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-7200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>8600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>42600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>14400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-53800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>61700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>65800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>20900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-10200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>8000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>1200</v>
       </c>
-      <c r="W102" s="3" t="s">
+      <c r="Y102" s="3" t="s">
         <v>12</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BVS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BVS_QTR_FIN.xlsx
@@ -656,328 +656,341 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E7" s="2">
         <v>45381</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45108</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45017</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44835</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44744</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44653</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44471</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44380</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44289</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44100</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44009</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43918</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43645</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>42735</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>42462</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>42369</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>151200</v>
+      </c>
+      <c r="E8" s="3">
         <v>129500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>135400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>120800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>137100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>119100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>125800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>128700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>140300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>117300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>130400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>108900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>109800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>81800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>98600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>85900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>136700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>78600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>97600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>160300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>274500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>65400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>71200</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>47600</v>
+      </c>
+      <c r="E9" s="3">
         <v>41100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>49100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>41900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>47900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>45100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>51600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>44100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>43700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>41600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>42600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>29800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>33500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>22200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>25100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>23400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>39100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>21400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>24100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>45100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>80400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>19200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>20200</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>103600</v>
+      </c>
+      <c r="E10" s="3">
         <v>88400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>86300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>78900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>89200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>74000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>74200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>84600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>96600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>75700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>87800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>79100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>76300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>59600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>73500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>62500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>97600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>57200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>73500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>115200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>194100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>46200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>51000</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1003,79 +1016,83 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E12" s="3">
         <v>2600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>3300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>3000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>3400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>3800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>5900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>4600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>6400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>6900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>7100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>6200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>4800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>2900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>3600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>4700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>2100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>3100</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>5100</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>7900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>3700</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1145,114 +1162,120 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>31900</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>1100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>78900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>4600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>314500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>3900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>5700</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="R14" s="3">
         <v>900</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-2300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>3500</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="V14" s="3">
         <v>3300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>500</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>8800</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>200</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E15" s="3">
         <v>1800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2100</v>
-      </c>
-      <c r="F15" s="3">
-        <v>2300</v>
       </c>
       <c r="G15" s="3">
         <v>2300</v>
       </c>
       <c r="H15" s="3">
+        <v>2300</v>
+      </c>
+      <c r="I15" s="3">
         <v>2100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>3300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2700</v>
-      </c>
-      <c r="N15" s="3">
-        <v>1900</v>
       </c>
       <c r="O15" s="3">
         <v>1900</v>
@@ -1261,34 +1284,37 @@
         <v>1900</v>
       </c>
       <c r="Q15" s="3">
+        <v>1900</v>
+      </c>
+      <c r="R15" s="3">
         <v>2100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>1700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>3600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>1800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>2100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>3800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>11000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>2800</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1311,150 +1337,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>180600</v>
+      </c>
+      <c r="E17" s="3">
         <v>124100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>134300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>118400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>130300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>211100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>141500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>255500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>143600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>138700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>133600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>112100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>115600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>59800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>92700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>75900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>127200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>65700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>86800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>153500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>263600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>67400</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-29400</v>
+      </c>
+      <c r="E18" s="3">
         <v>5400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>6800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-92000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-15700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-126800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-3300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-21400</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-3200</v>
       </c>
       <c r="N18" s="3">
         <v>-3200</v>
       </c>
       <c r="O18" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="P18" s="3">
         <v>-5800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>22000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>5900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>10000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>9500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>12900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>10800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>6900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>10900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1480,8 +1513,9 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1489,173 +1523,179 @@
         <v>-500</v>
       </c>
       <c r="E20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F20" s="3">
         <v>700</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-500</v>
       </c>
       <c r="G20" s="3">
         <v>-500</v>
       </c>
       <c r="H20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I20" s="3">
         <v>1500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-9400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-3200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1400</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-3300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>2400</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>300</v>
       </c>
       <c r="R20" s="3">
         <v>300</v>
       </c>
       <c r="S20" s="3">
+        <v>300</v>
+      </c>
+      <c r="T20" s="3">
         <v>-1900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-2400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-600</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>-700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>500</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-16800</v>
+      </c>
+      <c r="E21" s="3">
         <v>16700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>14300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>15800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>20800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-74000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-1900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-108200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>5900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-7100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>7100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>5400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>31600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>13000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>17500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>22200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>17800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>17500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>22600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>44000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>7600</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E22" s="3">
         <v>10000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>10300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>10100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>10600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>9700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>7400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>3600</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>12</v>
+      <c r="M22" s="3">
+        <v>0</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>12</v>
@@ -1666,177 +1706,186 @@
       <c r="P22" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="R22" s="3">
         <v>3000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>1900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>3200</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="U22" s="3">
+      <c r="U22" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="V22" s="3">
         <v>3900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>9400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>15900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>3900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-39500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-5100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-8400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-8200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-4400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-100200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-32400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-130600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-6500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-19500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-4600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-3200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-9100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>24500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>8300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>4400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>10500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>6200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-2500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-5700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-5400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-5300</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="E24" s="3">
         <v>900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-11000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-29500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-5100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-2700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-100</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
       <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
         <v>900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1906,150 +1955,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-32100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-6000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-7700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-8800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-4700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-100000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-21500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-101000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-7700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-14400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-10800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>24500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>8000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>4500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>10500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>5300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-2800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-6700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-6000</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-24000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-4600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-6100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-7300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-3700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-79700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-13200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-72800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-7000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-10900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-4100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>24900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>3000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>10900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-5700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-12200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-7100</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2119,8 +2177,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2137,25 +2198,25 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>-59500</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-18700</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-35400</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-300</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-400</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>12</v>
+      <c r="N29" s="3">
+        <v>0</v>
       </c>
       <c r="O29" s="3" t="s">
         <v>12</v>
@@ -2163,8 +2224,8 @@
       <c r="P29" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="R29" s="3">
         <v>0</v>
@@ -2172,26 +2233,29 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="U29" s="3">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="V29" s="3">
         <v>-200</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-1600</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-11200</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="Y29" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2261,8 +2325,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2332,8 +2399,11 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2341,141 +2411,147 @@
         <v>500</v>
       </c>
       <c r="E32" s="3">
+        <v>500</v>
+      </c>
+      <c r="F32" s="3">
         <v>-700</v>
-      </c>
-      <c r="F32" s="3">
-        <v>500</v>
       </c>
       <c r="G32" s="3">
         <v>500</v>
       </c>
       <c r="H32" s="3">
+        <v>500</v>
+      </c>
+      <c r="I32" s="3">
         <v>-1500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>9400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>3200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1400</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>3300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-2400</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-300</v>
       </c>
       <c r="R32" s="3">
         <v>-300</v>
       </c>
       <c r="S32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="T32" s="3">
         <v>1900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>2400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>600</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-500</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-24000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-4600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-6100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-7300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-3700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-139200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-31900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-108200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-7300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-11300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-4100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>24900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>3000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>10900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-7400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-23400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-7100</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2545,155 +2621,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-24000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-4600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-6100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-7300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-3700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-139200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-31900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-108200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-7300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-11300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-4100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>24900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>3000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>10900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-7400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-23400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-7100</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E38" s="2">
         <v>45381</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45108</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45017</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44835</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44744</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44653</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44471</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44380</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44289</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44100</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44009</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43918</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43645</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>42735</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>42462</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>42369</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2719,8 +2804,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2746,62 +2832,63 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E41" s="3">
         <v>25200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>37000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>26800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>29400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>47100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>30200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>34400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>41000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>27400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>43900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>80900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>136100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>124200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>86800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>72500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>126200</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>12</v>
       </c>
@@ -2817,8 +2904,11 @@
       <c r="Y41" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2888,62 +2978,65 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>137300</v>
+      </c>
+      <c r="E43" s="3">
         <v>125500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>123000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>112900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>119600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>118500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>136600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>132200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>143000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>119300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>125000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>105400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>102000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>89500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>88400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>80900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>67400</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>12</v>
       </c>
@@ -2959,62 +3052,65 @@
       <c r="Y43" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>87600</v>
+      </c>
+      <c r="E44" s="3">
         <v>97000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>91300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>97600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>96300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>88000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>82900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>77000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>69100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>64700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>61700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>36600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>34000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>39800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>29100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>34700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>33800</v>
       </c>
-      <c r="T44" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="U44" s="3" t="s">
         <v>12</v>
       </c>
@@ -3030,62 +3126,65 @@
       <c r="Y44" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>52000</v>
+      </c>
+      <c r="E45" s="3">
         <v>18200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>16700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>12200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>15300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>55100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>21100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>27600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>24100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>34000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>32400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>23200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>17900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>17200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>7500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>5000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>7100</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>12</v>
       </c>
@@ -3101,62 +3200,65 @@
       <c r="Y45" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>308900</v>
+      </c>
+      <c r="E46" s="3">
         <v>265900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>268000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>249500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>260600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>308700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>272600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>271100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>277200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>245400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>263100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>246100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>290100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>270700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>211800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>193100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>234400</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>12</v>
       </c>
@@ -3172,62 +3274,65 @@
       <c r="Y46" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E47" s="3">
         <v>3200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>3100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>6900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>6500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>5300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>13000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>78500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>28800</v>
-      </c>
-      <c r="M47" s="3">
-        <v>29300</v>
       </c>
       <c r="N47" s="3">
         <v>29300</v>
       </c>
       <c r="O47" s="3">
+        <v>29300</v>
+      </c>
+      <c r="P47" s="3">
         <v>19500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>21200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>19400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>19900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>3400</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="U47" s="3" t="s">
         <v>12</v>
       </c>
@@ -3243,62 +3348,65 @@
       <c r="Y47" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>42300</v>
+      </c>
+      <c r="E48" s="3">
         <v>47000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>50000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>54000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>57100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>52600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>44100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>42900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>43500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>43600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>40200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>27200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>26600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>26100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>21800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>19800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>18900</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>12</v>
       </c>
@@ -3314,62 +3422,65 @@
       <c r="Y48" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>432000</v>
+      </c>
+      <c r="E49" s="3">
         <v>478100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>489800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>500800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>512700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>523500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>647300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1071000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>809700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>829300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>842800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>301700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>310000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>324600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>241500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>246500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>252700</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="U49" s="3" t="s">
         <v>12</v>
       </c>
@@ -3385,8 +3496,11 @@
       <c r="Y49" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3456,8 +3570,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3527,19 +3644,22 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>12</v>
+      <c r="D52" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F52" s="3">
+        <v>0</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>12</v>
@@ -3547,32 +3667,32 @@
       <c r="H52" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I52" s="3">
+      <c r="I52" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J52" s="3">
         <v>406000</v>
       </c>
-      <c r="J52" s="3">
-        <v>0</v>
-      </c>
       <c r="K52" s="3">
         <v>0</v>
       </c>
       <c r="L52" s="3">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3">
         <v>50000</v>
-      </c>
-      <c r="M52" s="3">
-        <v>50500</v>
       </c>
       <c r="N52" s="3">
         <v>50500</v>
       </c>
       <c r="O52" s="3">
-        <v>500</v>
+        <v>50500</v>
       </c>
       <c r="P52" s="3">
         <v>500</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>12</v>
+      <c r="Q52" s="3">
+        <v>500</v>
       </c>
       <c r="R52" s="3" t="s">
         <v>12</v>
@@ -3589,8 +3709,8 @@
       <c r="V52" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="W52" s="3">
-        <v>0</v>
+      <c r="W52" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="X52" s="3">
         <v>0</v>
@@ -3598,8 +3718,11 @@
       <c r="Y52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3669,62 +3792,65 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>792200</v>
+      </c>
+      <c r="E54" s="3">
         <v>794200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>810900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>811100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>837000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>887400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1372600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1398000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1208800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1197100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1225900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>654800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>646600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>643100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>494500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>479300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>509400</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>12</v>
       </c>
@@ -3740,8 +3866,11 @@
       <c r="Y54" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3767,8 +3896,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3794,62 +3924,63 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>24400</v>
+      </c>
+      <c r="E57" s="3">
         <v>19100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>23000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>17600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>41400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>32800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>36700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>19100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>25700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>22500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>16900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>10900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>9900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>10300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>8800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>13600</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>12</v>
       </c>
@@ -3865,43 +3996,46 @@
       <c r="Y57" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>38600</v>
+      </c>
+      <c r="E58" s="3">
         <v>35800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>27800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>19600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>11300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>41300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>33100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>31300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>22500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>20300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>18000</v>
-      </c>
-      <c r="N58" s="3">
-        <v>15000</v>
       </c>
       <c r="O58" s="3">
         <v>15000</v>
@@ -3913,14 +4047,14 @@
         <v>15000</v>
       </c>
       <c r="R58" s="3">
+        <v>15000</v>
+      </c>
+      <c r="S58" s="3">
         <v>16300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>15000</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>12</v>
       </c>
@@ -3936,62 +4070,65 @@
       <c r="Y58" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>168500</v>
+      </c>
+      <c r="E59" s="3">
         <v>118400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>124600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>123600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>126400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>121900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>351900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>238000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>150600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>128700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>145900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>134800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>133300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>123700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>103200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>86700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>68700</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>12</v>
       </c>
@@ -4007,62 +4144,65 @@
       <c r="Y59" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>231500</v>
+      </c>
+      <c r="E60" s="3">
         <v>173300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>175500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>160800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>179100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>196100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>304000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>288400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>198900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>171500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>180900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>160700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>158200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>149000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>122600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>111700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>97200</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>12</v>
       </c>
@@ -4078,62 +4218,65 @@
       <c r="Y60" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>344700</v>
+      </c>
+      <c r="E61" s="3">
         <v>355400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>367000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>375000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>374600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>404300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>385000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>393100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>351400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>348000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>339600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>162400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>166100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>169700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>173400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>177000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>229700</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -4149,62 +4292,65 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>26900</v>
+      </c>
+      <c r="E62" s="3">
         <v>48100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>47300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>48800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>49900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>46700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>350700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>337400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>138300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>155700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>171600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>101200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>103000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>104000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>54300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>45200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>40700</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>12</v>
       </c>
@@ -4220,8 +4366,11 @@
       <c r="Y62" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4291,8 +4440,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4362,8 +4514,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4433,62 +4588,65 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>641200</v>
+      </c>
+      <c r="E66" s="3">
         <v>623000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>637300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>633600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>653800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>698900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1047400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1054600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>760800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>747400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>766900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>502300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>505100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>500700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>352200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>336100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>370200</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>12</v>
       </c>
@@ -4504,8 +4662,11 @@
       <c r="Y66" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4531,8 +4692,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4602,8 +4764,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4673,8 +4838,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4718,7 +4886,7 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3">
-        <v>168000</v>
+        <v>0</v>
       </c>
       <c r="R70" s="3">
         <v>168000</v>
@@ -4727,7 +4895,7 @@
         <v>168000</v>
       </c>
       <c r="T70" s="3">
-        <v>0</v>
+        <v>168000</v>
       </c>
       <c r="U70" s="3">
         <v>0</v>
@@ -4744,8 +4912,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4815,62 +4986,65 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-350100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-326100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-321500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-315400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-308100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-304500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-165300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-133400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-25100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-17900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-6600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-6200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-5200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-140700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-138400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-141500</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>12</v>
       </c>
@@ -4886,8 +5060,11 @@
       <c r="Y72" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4957,8 +5134,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5028,8 +5208,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5099,62 +5282,65 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>150900</v>
+      </c>
+      <c r="E76" s="3">
         <v>171300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>173600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>177500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>183200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>188500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>325200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>343400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>448000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>449800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>458900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>152500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>141600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>142400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-25800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-24800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-28800</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>12</v>
       </c>
@@ -5170,8 +5356,11 @@
       <c r="Y76" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5241,155 +5430,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E80" s="2">
         <v>45381</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45108</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45017</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44835</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44744</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44653</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44471</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44380</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44289</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44100</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44009</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43918</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43645</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>42735</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>42462</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>42369</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-24000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-4600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-6100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-7300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-3700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-139200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-31900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-108200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-7300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-11300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-4100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>24900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>3000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>10900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-7400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-23400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-7100</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5415,79 +5613,83 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E83" s="3">
         <v>11800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>12500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>13800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>14600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>16500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>23200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>18800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>12400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>12500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>11700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>8500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>7500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>7200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>6900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>7300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>14500</v>
-      </c>
-      <c r="T83" s="3">
-        <v>7300</v>
       </c>
       <c r="U83" s="3">
         <v>7300</v>
       </c>
       <c r="V83" s="3">
+        <v>7300</v>
+      </c>
+      <c r="W83" s="3">
         <v>15700</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="X83" s="3">
+      <c r="X83" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y83" s="3">
         <v>9100</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5557,8 +5759,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5628,8 +5833,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5699,8 +5907,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5770,8 +5981,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5841,79 +6055,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-6000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>10400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-8300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>10800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>5200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-21000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>13100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>10600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>17300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-18000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>25400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>20800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>25500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>17700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>21000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>8000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>37100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>2200</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5939,79 +6159,83 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1300</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="X91" s="3">
+      <c r="X91" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-600</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6081,8 +6305,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6152,79 +6379,85 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>33500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-15100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-56300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-52000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-221300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-13200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-46600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-17800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-7300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-7900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-6600</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6250,8 +6483,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6321,8 +6555,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6392,8 +6629,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6463,8 +6703,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6534,217 +6777,229 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-4200</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>8200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-62200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>27400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-5400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>50700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>7700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>9200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>176300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-4300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-6100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>107500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-9900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-57100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>37400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>48800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-11100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-9000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>5500</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E101" s="3">
         <v>-500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1100</v>
-      </c>
-      <c r="J101" s="3">
-        <v>-200</v>
       </c>
       <c r="K101" s="3">
         <v>-200</v>
       </c>
       <c r="L101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-200</v>
-      </c>
-      <c r="T101" s="3">
-        <v>-300</v>
       </c>
       <c r="U101" s="3">
         <v>-300</v>
       </c>
       <c r="V101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="W101" s="3">
         <v>300</v>
       </c>
-      <c r="W101" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="X101" s="3">
+      <c r="X101" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y101" s="3">
         <v>200</v>
       </c>
-      <c r="Y101" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-11800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>10100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-17700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>15300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-6600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-41700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-16600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-31700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-7200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>8600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>42600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>14400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-53800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>61700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>65800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>20900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-10200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>8000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1200</v>
       </c>
-      <c r="Y102" s="3" t="s">
+      <c r="Z102" s="3" t="s">
         <v>12</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BVS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BVS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="92">
   <si>
     <t>BVS</t>
   </si>
@@ -656,341 +656,354 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E7" s="2">
         <v>45472</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45381</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45108</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45017</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44835</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44744</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44653</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44471</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44380</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44289</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44100</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44009</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43918</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43645</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>42735</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>42462</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>42369</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>139000</v>
+      </c>
+      <c r="E8" s="3">
         <v>151200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>129500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>135400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>120800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>137100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>119100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>125800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>128700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>140300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>117300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>130400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>108900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>109800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>81800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>98600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>85900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>136700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>78600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>97600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>160300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>274500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>65400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>71200</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>45400</v>
+      </c>
+      <c r="E9" s="3">
         <v>47600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>41100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>49100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>41900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>47900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>45100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>51600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>44100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>43700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>41600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>42600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>29800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>33500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>22200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>25100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>23400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>39100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>21400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>24100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>45100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>80400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>19200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>20200</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>93600</v>
+      </c>
+      <c r="E10" s="3">
         <v>103600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>88400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>86300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>78900</v>
       </c>
-      <c r="H10" s="3">
-        <v>89200</v>
-      </c>
       <c r="I10" s="3">
-        <v>74000</v>
+        <v>89100</v>
       </c>
       <c r="J10" s="3">
+        <v>73900</v>
+      </c>
+      <c r="K10" s="3">
         <v>74200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>84600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>96600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>75700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>87800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>79100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>76300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>59600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>73500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>62500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>97600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>57200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>73500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>115200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>194100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>46200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>51000</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1017,82 +1030,86 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E12" s="3">
         <v>4000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>2600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>3300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>3000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>3400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>3800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>5900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>4600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>6400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>6900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>7100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>6200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>4800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>2900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>3600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>4700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>2100</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>3100</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>5100</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>7900</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>3700</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1165,82 +1182,88 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>31900</v>
+        <v>2600</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>44700</v>
       </c>
       <c r="F14" s="3">
-        <v>1100</v>
+        <v>300</v>
       </c>
       <c r="G14" s="3">
-        <v>1400</v>
+        <v>-100</v>
       </c>
       <c r="H14" s="3">
-        <v>1600</v>
+        <v>1300</v>
       </c>
       <c r="I14" s="3">
-        <v>78900</v>
+        <v>1800</v>
       </c>
       <c r="J14" s="3">
+        <v>77700</v>
+      </c>
+      <c r="K14" s="3">
         <v>4600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>314500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>3900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>5700</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="S14" s="3">
         <v>900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-2300</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>3500</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="V14" s="3">
+      <c r="V14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="W14" s="3">
         <v>3300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>500</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>8800</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>200</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1248,37 +1271,37 @@
         <v>2100</v>
       </c>
       <c r="E15" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F15" s="3">
         <v>1800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2100</v>
-      </c>
-      <c r="G15" s="3">
-        <v>2300</v>
       </c>
       <c r="H15" s="3">
         <v>2300</v>
       </c>
       <c r="I15" s="3">
+        <v>2300</v>
+      </c>
+      <c r="J15" s="3">
         <v>2100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>3300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>2700</v>
-      </c>
-      <c r="O15" s="3">
-        <v>1900</v>
       </c>
       <c r="P15" s="3">
         <v>1900</v>
@@ -1287,34 +1310,37 @@
         <v>1900</v>
       </c>
       <c r="R15" s="3">
+        <v>1900</v>
+      </c>
+      <c r="S15" s="3">
         <v>2100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>1700</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>3600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>1800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>2100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>3800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>11000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>2800</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1338,156 +1364,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>180600</v>
+        <v>132300</v>
       </c>
       <c r="E17" s="3">
-        <v>124100</v>
+        <v>135900</v>
       </c>
       <c r="F17" s="3">
-        <v>134300</v>
+        <v>123800</v>
       </c>
       <c r="G17" s="3">
-        <v>118400</v>
+        <v>132800</v>
       </c>
       <c r="H17" s="3">
-        <v>130300</v>
+        <v>117100</v>
       </c>
       <c r="I17" s="3">
-        <v>211100</v>
+        <v>128500</v>
       </c>
       <c r="J17" s="3">
+        <v>131900</v>
+      </c>
+      <c r="K17" s="3">
         <v>141500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>255500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>143600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>138700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>133600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>112100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>115600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>59800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>92700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>75900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>127200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>65700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>86800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>153500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>263600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>67400</v>
       </c>
-      <c r="Z17" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-29400</v>
+        <v>6600</v>
       </c>
       <c r="E18" s="3">
-        <v>5400</v>
+        <v>15300</v>
       </c>
       <c r="F18" s="3">
-        <v>1100</v>
+        <v>5600</v>
       </c>
       <c r="G18" s="3">
-        <v>2400</v>
+        <v>2600</v>
       </c>
       <c r="H18" s="3">
-        <v>6800</v>
+        <v>3700</v>
       </c>
       <c r="I18" s="3">
-        <v>-92000</v>
+        <v>8600</v>
       </c>
       <c r="J18" s="3">
+        <v>-12800</v>
+      </c>
+      <c r="K18" s="3">
         <v>-15700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-126800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-3300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-21400</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-3200</v>
       </c>
       <c r="O18" s="3">
         <v>-3200</v>
       </c>
       <c r="P18" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="Q18" s="3">
         <v>-5800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>22000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>5900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>10000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>9500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>12900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>10800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>6900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>10900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1514,156 +1547,163 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-500</v>
+        <v>-600</v>
       </c>
       <c r="E20" s="3">
-        <v>-500</v>
+        <v>200</v>
       </c>
       <c r="F20" s="3">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="G20" s="3">
-        <v>-500</v>
+        <v>800</v>
       </c>
       <c r="H20" s="3">
-        <v>-500</v>
+        <v>500</v>
       </c>
       <c r="I20" s="3">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="J20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K20" s="3">
         <v>-9400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-3200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1400</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2400</v>
-      </c>
-      <c r="R20" s="3">
-        <v>300</v>
       </c>
       <c r="S20" s="3">
         <v>300</v>
       </c>
       <c r="T20" s="3">
+        <v>300</v>
+      </c>
+      <c r="U20" s="3">
         <v>-1900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-2400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-600</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>500</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-16800</v>
+        <v>9300</v>
       </c>
       <c r="E21" s="3">
-        <v>16700</v>
+        <v>17200</v>
       </c>
       <c r="F21" s="3">
-        <v>14300</v>
+        <v>7300</v>
       </c>
       <c r="G21" s="3">
-        <v>15800</v>
+        <v>3900</v>
       </c>
       <c r="H21" s="3">
-        <v>20800</v>
+        <v>5500</v>
       </c>
       <c r="I21" s="3">
-        <v>-74000</v>
+        <v>10400</v>
       </c>
       <c r="J21" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="K21" s="3">
         <v>-1900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-108200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>5900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-7100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>7100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>5400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>31600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>13000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>17500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>22200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>17800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>17500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>22600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>44000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>7600</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1671,34 +1711,34 @@
         <v>9500</v>
       </c>
       <c r="E22" s="3">
-        <v>10000</v>
+        <v>9900</v>
       </c>
       <c r="F22" s="3">
         <v>10300</v>
       </c>
       <c r="G22" s="3">
+        <v>10300</v>
+      </c>
+      <c r="H22" s="3">
         <v>10100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>10600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>9700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>7400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>3600</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>12</v>
+      <c r="N22" s="3">
+        <v>0</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>12</v>
@@ -1709,183 +1749,192 @@
       <c r="Q22" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="R22" s="3">
+      <c r="R22" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="S22" s="3">
         <v>3000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>1900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>3200</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="V22" s="3">
+      <c r="V22" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="W22" s="3">
         <v>3900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>9400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>15900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>3900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-39500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-5100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-8400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-8200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-4400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-100200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-32400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-130600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-6500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-19500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-4600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-3200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-9100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>24500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>3100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>8300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>4400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>10500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>6200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-2500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-5700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-5400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-5300</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>600</v>
+      </c>
+      <c r="E24" s="3">
         <v>-7300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-11000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-29500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-5100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-2700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-100</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
       <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
         <v>900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1958,156 +2007,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-32100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-6000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-7700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-8800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-4700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-100000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-21500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-101000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-7700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-14400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-10800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>24500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>8000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>4500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>10500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>5300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-2800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-6700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-6000</v>
       </c>
-      <c r="Z26" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-24000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-4600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-6100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-7300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-3700</v>
       </c>
-      <c r="I27" s="3">
-        <v>-79700</v>
-      </c>
       <c r="J27" s="3">
+        <v>-139200</v>
+      </c>
+      <c r="K27" s="3">
         <v>-13200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-72800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-7000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-10900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>24900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>3000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>10900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-5700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-12200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-7100</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2180,8 +2238,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2201,25 +2262,25 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>-59500</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-18700</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-35400</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-300</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-400</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
-      </c>
-      <c r="O29" s="3" t="s">
-        <v>12</v>
+      <c r="O29" s="3">
+        <v>0</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>12</v>
@@ -2227,8 +2288,8 @@
       <c r="Q29" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
+      <c r="R29" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="S29" s="3">
         <v>0</v>
@@ -2236,26 +2297,29 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="V29" s="3">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="W29" s="3">
         <v>-200</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-1600</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-11200</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="Z29" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2328,8 +2392,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2402,156 +2469,165 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="E32" s="3">
-        <v>500</v>
+        <v>-200</v>
       </c>
       <c r="F32" s="3">
-        <v>-700</v>
+        <v>-100</v>
       </c>
       <c r="G32" s="3">
-        <v>500</v>
+        <v>-800</v>
       </c>
       <c r="H32" s="3">
-        <v>500</v>
+        <v>-500</v>
       </c>
       <c r="I32" s="3">
-        <v>-1500</v>
+        <v>-500</v>
       </c>
       <c r="J32" s="3">
+        <v>100</v>
+      </c>
+      <c r="K32" s="3">
         <v>9400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>3200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1400</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>3300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2400</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-300</v>
       </c>
       <c r="S32" s="3">
         <v>-300</v>
       </c>
       <c r="T32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="U32" s="3">
         <v>1900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>2400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>600</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-500</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-24000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-4600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-6100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-7300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-3700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-139200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-31900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-108200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-7300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-11300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>24900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>3000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>10900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-7400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-23400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-7100</v>
       </c>
-      <c r="Z33" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2624,161 +2700,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-24000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-4600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-6100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-7300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-3700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-139200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-31900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-108200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-7300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-11300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>24900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>3000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>10900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-7400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-23400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-7100</v>
       </c>
-      <c r="Z35" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E38" s="2">
         <v>45472</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45381</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45108</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45017</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44835</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44744</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44653</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44471</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44380</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44289</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44100</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44009</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43918</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43645</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>42735</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>42462</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>42369</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2805,8 +2890,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2833,65 +2919,66 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>43100</v>
+      </c>
+      <c r="E41" s="3">
         <v>32000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>25200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>37000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>26800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>29400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>47100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>30200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>34400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>41000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>27400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>43900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>80900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>136100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>124200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>86800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>72500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>126200</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>12</v>
       </c>
@@ -2907,8 +2994,11 @@
       <c r="Z41" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2981,65 +3071,68 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>121900</v>
+      </c>
+      <c r="E43" s="3">
         <v>137300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>125500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>123000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>112900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>119600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>118500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>136600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>132200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>143000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>119300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>125000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>105400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>102000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>89500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>88400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>80900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>67400</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>12</v>
       </c>
@@ -3055,65 +3148,68 @@
       <c r="Z43" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>90000</v>
+      </c>
+      <c r="E44" s="3">
         <v>87600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>97000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>91300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>97600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>96300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>88000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>82900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>77000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>69100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>64700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>61700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>36600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>34000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>39800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>29100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>34700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>33800</v>
       </c>
-      <c r="U44" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="V44" s="3" t="s">
         <v>12</v>
       </c>
@@ -3129,65 +3225,68 @@
       <c r="Z44" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>52000</v>
+        <v>26700</v>
       </c>
       <c r="E45" s="3">
-        <v>18200</v>
-      </c>
-      <c r="F45" s="3">
-        <v>16700</v>
-      </c>
-      <c r="G45" s="3">
-        <v>12200</v>
-      </c>
-      <c r="H45" s="3">
-        <v>15300</v>
-      </c>
-      <c r="I45" s="3">
-        <v>55100</v>
+        <v>28400</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="J45" s="3">
+        <v>37900</v>
+      </c>
+      <c r="K45" s="3">
         <v>21100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>27600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>24100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>34000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>32400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>23200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>17900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>17200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>7500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>5000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>7100</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>12</v>
       </c>
@@ -3203,65 +3302,68 @@
       <c r="Z45" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>298700</v>
+      </c>
+      <c r="E46" s="3">
         <v>308900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>265900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>268000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>249500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>260600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>308700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>272600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>271100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>277200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>245400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>263100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>246100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>290100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>270700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>211800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>193100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>234400</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>12</v>
       </c>
@@ -3277,65 +3379,68 @@
       <c r="Z46" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E47" s="3">
         <v>2100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>3200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>3100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>6900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>6500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>5300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>13000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>78500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>28800</v>
-      </c>
-      <c r="N47" s="3">
-        <v>29300</v>
       </c>
       <c r="O47" s="3">
         <v>29300</v>
       </c>
       <c r="P47" s="3">
+        <v>29300</v>
+      </c>
+      <c r="Q47" s="3">
         <v>19500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>21200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>19400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>19900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>3400</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="V47" s="3" t="s">
         <v>12</v>
       </c>
@@ -3351,65 +3456,68 @@
       <c r="Z47" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>39200</v>
+      </c>
+      <c r="E48" s="3">
         <v>42300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>47000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>50000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>54000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>57100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>52600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>44100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>42900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>43500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>43600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>40200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>27200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>26600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>26100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>21800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>19800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>18900</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>12</v>
       </c>
@@ -3425,65 +3533,68 @@
       <c r="Z48" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>422300</v>
+      </c>
+      <c r="E49" s="3">
         <v>432000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>478100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>489800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>500800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>512700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>523500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>647300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1071000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>809700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>829300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>842800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>301700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>310000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>324600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>241500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>246500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>252700</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="V49" s="3" t="s">
         <v>12</v>
       </c>
@@ -3499,8 +3610,11 @@
       <c r="Z49" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3573,8 +3687,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3647,19 +3764,22 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>6900</v>
+      <c r="D52" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F52" s="3">
-        <v>0</v>
+      <c r="F52" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>12</v>
@@ -3670,32 +3790,32 @@
       <c r="I52" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="J52" s="3">
+      <c r="J52" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K52" s="3">
         <v>406000</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
       <c r="L52" s="3">
         <v>0</v>
       </c>
       <c r="M52" s="3">
+        <v>0</v>
+      </c>
+      <c r="N52" s="3">
         <v>50000</v>
-      </c>
-      <c r="N52" s="3">
-        <v>50500</v>
       </c>
       <c r="O52" s="3">
         <v>50500</v>
       </c>
       <c r="P52" s="3">
-        <v>500</v>
+        <v>50500</v>
       </c>
       <c r="Q52" s="3">
         <v>500</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>12</v>
+      <c r="R52" s="3">
+        <v>500</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>12</v>
@@ -3712,8 +3832,8 @@
       <c r="W52" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="X52" s="3">
-        <v>0</v>
+      <c r="X52" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="Y52" s="3">
         <v>0</v>
@@ -3721,8 +3841,11 @@
       <c r="Z52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3795,65 +3918,68 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>769500</v>
+      </c>
+      <c r="E54" s="3">
         <v>792200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>794200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>810900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>811100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>837000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>887400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1372600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1398000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1208800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1197100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1225900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>654800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>646600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>643100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>494500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>479300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>509400</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>12</v>
       </c>
@@ -3869,8 +3995,11 @@
       <c r="Z54" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3897,8 +4026,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3925,65 +4055,66 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E57" s="3">
         <v>24400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>19100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>23000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>17600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>41400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>32800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>36700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>19100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>25700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>22500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>16900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>10900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>9900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>10300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>8800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>13600</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>12</v>
       </c>
@@ -3999,46 +4130,49 @@
       <c r="Z57" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>38600</v>
+        <v>42500</v>
       </c>
       <c r="E58" s="3">
-        <v>35800</v>
+        <v>42400</v>
       </c>
       <c r="F58" s="3">
-        <v>27800</v>
+        <v>40600</v>
       </c>
       <c r="G58" s="3">
-        <v>19600</v>
+        <v>32700</v>
       </c>
       <c r="H58" s="3">
-        <v>11300</v>
+        <v>24300</v>
       </c>
       <c r="I58" s="3">
-        <v>41300</v>
+        <v>15300</v>
       </c>
       <c r="J58" s="3">
+        <v>45600</v>
+      </c>
+      <c r="K58" s="3">
         <v>33100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>31300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>22500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>20300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>18000</v>
-      </c>
-      <c r="O58" s="3">
-        <v>15000</v>
       </c>
       <c r="P58" s="3">
         <v>15000</v>
@@ -4050,14 +4184,14 @@
         <v>15000</v>
       </c>
       <c r="S58" s="3">
+        <v>15000</v>
+      </c>
+      <c r="T58" s="3">
         <v>16300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>15000</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="V58" s="3" t="s">
         <v>12</v>
       </c>
@@ -4073,65 +4207,68 @@
       <c r="Z58" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>168500</v>
+        <v>97900</v>
       </c>
       <c r="E59" s="3">
-        <v>118400</v>
+        <v>115600</v>
       </c>
       <c r="F59" s="3">
-        <v>124600</v>
+        <v>68900</v>
       </c>
       <c r="G59" s="3">
-        <v>123600</v>
+        <v>64300</v>
       </c>
       <c r="H59" s="3">
-        <v>126400</v>
+        <v>74300</v>
       </c>
       <c r="I59" s="3">
-        <v>121900</v>
+        <v>74200</v>
       </c>
       <c r="J59" s="3">
+        <v>72900</v>
+      </c>
+      <c r="K59" s="3">
         <v>351900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>238000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>150600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>128700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>145900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>134800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>133300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>123700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>103200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>86700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>68700</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>12</v>
       </c>
@@ -4147,65 +4284,68 @@
       <c r="Z59" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>211500</v>
+      </c>
+      <c r="E60" s="3">
         <v>231500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>173300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>175500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>160800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>179100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>196100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>304000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>288400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>198900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>171500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>180900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>160700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>158200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>149000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>122600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>111700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>97200</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>12</v>
       </c>
@@ -4221,65 +4361,68 @@
       <c r="Z60" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>344700</v>
+        <v>362600</v>
       </c>
       <c r="E61" s="3">
-        <v>355400</v>
+        <v>363200</v>
       </c>
       <c r="F61" s="3">
-        <v>367000</v>
+        <v>375300</v>
       </c>
       <c r="G61" s="3">
-        <v>375000</v>
+        <v>388000</v>
       </c>
       <c r="H61" s="3">
-        <v>374600</v>
+        <v>397100</v>
       </c>
       <c r="I61" s="3">
-        <v>404300</v>
+        <v>387100</v>
       </c>
       <c r="J61" s="3">
+        <v>424300</v>
+      </c>
+      <c r="K61" s="3">
         <v>385000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>393100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>351400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>348000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>339600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>162400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>166100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>169700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>173400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>177000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>229700</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -4295,65 +4438,68 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E62" s="3">
+        <v>8500</v>
+      </c>
+      <c r="F62" s="3">
         <v>26900</v>
       </c>
-      <c r="E62" s="3">
-        <v>48100</v>
-      </c>
-      <c r="F62" s="3">
-        <v>47300</v>
-      </c>
       <c r="G62" s="3">
-        <v>48800</v>
+        <v>25100</v>
       </c>
       <c r="H62" s="3">
-        <v>49900</v>
+        <v>26700</v>
       </c>
       <c r="I62" s="3">
-        <v>46700</v>
+        <v>37500</v>
       </c>
       <c r="J62" s="3">
+        <v>26300</v>
+      </c>
+      <c r="K62" s="3">
         <v>350700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>337400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>138300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>155700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>171600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>101200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>103000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>104000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>54300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>45200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>40700</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>12</v>
       </c>
@@ -4369,8 +4515,11 @@
       <c r="Z62" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4443,8 +4592,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4517,8 +4669,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4591,65 +4746,68 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>641200</v>
+        <v>582700</v>
       </c>
       <c r="E66" s="3">
-        <v>623000</v>
+        <v>603100</v>
       </c>
       <c r="F66" s="3">
-        <v>637300</v>
+        <v>576800</v>
       </c>
       <c r="G66" s="3">
-        <v>633600</v>
+        <v>589800</v>
       </c>
       <c r="H66" s="3">
-        <v>653800</v>
+        <v>584600</v>
       </c>
       <c r="I66" s="3">
-        <v>698900</v>
+        <v>603600</v>
       </c>
       <c r="J66" s="3">
+        <v>647000</v>
+      </c>
+      <c r="K66" s="3">
         <v>1047400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1054600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>760800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>747400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>766900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>502300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>505100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>500700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>352200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>336100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>370200</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>12</v>
       </c>
@@ -4665,8 +4823,11 @@
       <c r="Z66" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4693,8 +4854,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4767,8 +4929,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4841,8 +5006,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4889,7 +5057,7 @@
         <v>0</v>
       </c>
       <c r="R70" s="3">
-        <v>168000</v>
+        <v>0</v>
       </c>
       <c r="S70" s="3">
         <v>168000</v>
@@ -4898,7 +5066,7 @@
         <v>168000</v>
       </c>
       <c r="U70" s="3">
-        <v>0</v>
+        <v>168000</v>
       </c>
       <c r="V70" s="3">
         <v>0</v>
@@ -4915,8 +5083,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4989,65 +5160,68 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-354900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-350100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-326100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-321500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-315400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-308100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-304500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-165300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-133400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-25100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-17900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-6600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-6200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-140700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-138400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-141500</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>12</v>
       </c>
@@ -5063,8 +5237,11 @@
       <c r="Z72" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5137,8 +5314,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5211,8 +5391,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5285,65 +5468,68 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>148700</v>
+      </c>
+      <c r="E76" s="3">
         <v>150900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>171300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>173600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>177500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>183200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>188500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>325200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>343400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>448000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>449800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>458900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>152500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>141600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>142400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-25800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-24800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-28800</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>12</v>
       </c>
@@ -5359,8 +5545,11 @@
       <c r="Z76" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5433,161 +5622,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E80" s="2">
         <v>45472</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45381</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45108</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45017</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44835</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44744</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44653</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44471</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44380</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44289</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44100</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44009</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43918</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43645</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>42735</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>42462</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>42369</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-24000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-4600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-6100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-7300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-3700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-139200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-31900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-108200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-7300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-11300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>24900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>3000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>10900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-7400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-23400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-7100</v>
       </c>
-      <c r="Z81" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5614,82 +5812,86 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>13100</v>
+        <v>13800</v>
       </c>
       <c r="E83" s="3">
-        <v>11800</v>
+        <v>14600</v>
       </c>
       <c r="F83" s="3">
+        <v>16500</v>
+      </c>
+      <c r="G83" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I83" s="3">
+        <v>12400</v>
+      </c>
+      <c r="J83" s="3">
         <v>12500</v>
       </c>
-      <c r="G83" s="3">
-        <v>13800</v>
-      </c>
-      <c r="H83" s="3">
-        <v>14600</v>
-      </c>
-      <c r="I83" s="3">
-        <v>16500</v>
-      </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>23200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>18800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>12400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>12500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>11700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>8500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>7500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>7200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>6900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>7300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>14500</v>
-      </c>
-      <c r="U83" s="3">
-        <v>7300</v>
       </c>
       <c r="V83" s="3">
         <v>7300</v>
       </c>
       <c r="W83" s="3">
+        <v>7300</v>
+      </c>
+      <c r="X83" s="3">
         <v>15700</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="Y83" s="3">
+      <c r="Y83" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z83" s="3">
         <v>9100</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5762,8 +5964,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5836,8 +6041,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5910,8 +6118,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5984,8 +6195,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6058,82 +6272,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E89" s="3">
         <v>15200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-6000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>10400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-8300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>10800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>5200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-21000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>13100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>10600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>17300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-18000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>25400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>20800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>25500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>17700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>21000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>8000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>37100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>2200</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6160,8 +6380,9 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6169,73 +6390,76 @@
         <v>-100</v>
       </c>
       <c r="E91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F91" s="3">
         <v>-300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1300</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="Y91" s="3">
+      <c r="Y91" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-600</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6308,8 +6532,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6382,8 +6609,11 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6391,73 +6621,76 @@
         <v>-100</v>
       </c>
       <c r="E94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F94" s="3">
         <v>-1000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>33500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-15100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-56300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-52000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-221300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-13200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-46600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-17800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-7300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-7900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-6600</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6484,31 +6717,32 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6558,8 +6792,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6632,8 +6869,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6706,8 +6946,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6780,82 +7023,88 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-7800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-4200</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>8200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-62200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>27400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-5400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>50700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>7700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>9200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>176300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-4300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>107500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-9900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-57100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>37400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>48800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-11100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-9000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>5500</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6863,143 +7112,149 @@
         <v>-400</v>
       </c>
       <c r="E101" s="3">
-        <v>-500</v>
+        <v>200</v>
       </c>
       <c r="F101" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="G101" s="3">
-        <v>-400</v>
-      </c>
-      <c r="H101" s="3">
-        <v>200</v>
+        <v>1100</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="I101" s="3">
-        <v>500</v>
+        <v>-200</v>
       </c>
       <c r="J101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K101" s="3">
         <v>1100</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-200</v>
       </c>
       <c r="L101" s="3">
         <v>-200</v>
       </c>
       <c r="M101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N101" s="3">
         <v>-100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-200</v>
-      </c>
-      <c r="U101" s="3">
-        <v>-300</v>
       </c>
       <c r="V101" s="3">
         <v>-300</v>
       </c>
       <c r="W101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="X101" s="3">
         <v>300</v>
       </c>
-      <c r="X101" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="Y101" s="3">
+      <c r="Y101" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z101" s="3">
         <v>200</v>
       </c>
-      <c r="Z101" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E102" s="3">
         <v>6800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-11800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>10100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-17700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>15300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-6600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-41700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-16600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-31700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-7200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>8600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>42600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>14400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-53800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>61700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>65800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>20900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-10200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>8000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1200</v>
       </c>
-      <c r="Z102" s="3" t="s">
+      <c r="AA102" s="3" t="s">
         <v>12</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BVS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BVS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="92">
   <si>
     <t>BVS</t>
   </si>
@@ -656,354 +656,366 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45563</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45472</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45381</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45108</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45017</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44835</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44744</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44653</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44471</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44380</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44289</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44100</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44009</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43918</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43645</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>42735</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>42462</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>42369</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>153600</v>
+      </c>
+      <c r="E8" s="3">
         <v>139000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>151200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>129500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>135400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>120800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>137100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>119100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>125800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>128700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>140300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>117300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>130400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>108900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>109800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>81800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>98600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>85900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>136700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>78600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>97600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>160300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>274500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>65400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>71200</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>51000</v>
+      </c>
+      <c r="E9" s="3">
         <v>45400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>47600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>41100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>49100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>41900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>47900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>45100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>51600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>44100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>43700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>41600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>42600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>29800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>33500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>22200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>25100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>23400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>39100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>21400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>24100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>45100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>80400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>19200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>20200</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>102700</v>
+      </c>
+      <c r="E10" s="3">
         <v>93600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>103600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>88400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>86300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>78900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>89100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>73900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>74200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>84600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>96600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>75700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>87800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>79100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>76300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>59600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>73500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>62500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>97600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>57200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>73500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>115200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>194100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>46200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>51000</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1031,85 +1043,89 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E12" s="3">
         <v>3800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>4000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>2600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>3300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>3000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>3400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>3800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>5900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>4600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>6400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>6900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>7100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>6200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>4800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>2900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>3600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>4700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>2100</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>3100</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>5100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>7900</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>3700</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1185,126 +1201,132 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E14" s="3">
         <v>2600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>44700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>300</v>
       </c>
-      <c r="G14" s="3">
-        <v>-100</v>
-      </c>
       <c r="H14" s="3">
+        <v>1400</v>
+      </c>
+      <c r="I14" s="3">
         <v>1300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>77700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>4600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>314500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>3900</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>5700</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="T14" s="3">
         <v>900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-2300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>3500</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="X14" s="3">
         <v>3300</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>500</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>8800</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>200</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>2100</v>
+        <v>1800</v>
       </c>
       <c r="E15" s="3">
         <v>2100</v>
       </c>
       <c r="F15" s="3">
+        <v>2100</v>
+      </c>
+      <c r="G15" s="3">
         <v>1800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>2100</v>
-      </c>
-      <c r="H15" s="3">
-        <v>2300</v>
       </c>
       <c r="I15" s="3">
         <v>2300</v>
       </c>
       <c r="J15" s="3">
+        <v>2300</v>
+      </c>
+      <c r="K15" s="3">
         <v>2100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>3300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>2700</v>
-      </c>
-      <c r="P15" s="3">
-        <v>1900</v>
       </c>
       <c r="Q15" s="3">
         <v>1900</v>
@@ -1313,34 +1335,37 @@
         <v>1900</v>
       </c>
       <c r="S15" s="3">
+        <v>1900</v>
+      </c>
+      <c r="T15" s="3">
         <v>2100</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>1700</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>3600</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>1800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>2100</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>3800</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>11000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>2800</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1365,162 +1390,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>142500</v>
+      </c>
+      <c r="E17" s="3">
         <v>132300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>135900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>123800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>132800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>117100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>128500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>131900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>141500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>255500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>143600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>138700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>133600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>112100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>115600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>59800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>92700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>75900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>127200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>65700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>86800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>153500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>263600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>67400</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E18" s="3">
         <v>6600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>15300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>5600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>8600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-12800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-15700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-126800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-3300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-21400</v>
-      </c>
-      <c r="O18" s="3">
-        <v>-3200</v>
       </c>
       <c r="P18" s="3">
         <v>-3200</v>
       </c>
       <c r="Q18" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="R18" s="3">
         <v>-5800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>22000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>5900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>10000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>9500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>12900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>10800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>6900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>10900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1548,200 +1580,207 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>100</v>
       </c>
-      <c r="G20" s="3">
-        <v>800</v>
-      </c>
       <c r="H20" s="3">
-        <v>500</v>
+        <v>-700</v>
       </c>
       <c r="I20" s="3">
         <v>500</v>
       </c>
       <c r="J20" s="3">
+        <v>500</v>
+      </c>
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-9400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-3200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1400</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-3300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>2400</v>
-      </c>
-      <c r="S20" s="3">
-        <v>300</v>
       </c>
       <c r="T20" s="3">
         <v>300</v>
       </c>
       <c r="U20" s="3">
+        <v>300</v>
+      </c>
+      <c r="V20" s="3">
         <v>-1900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-2400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-600</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>500</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E21" s="3">
         <v>9300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>17200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>7300</v>
       </c>
-      <c r="G21" s="3">
-        <v>3900</v>
-      </c>
       <c r="H21" s="3">
+        <v>5400</v>
+      </c>
+      <c r="I21" s="3">
         <v>5500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>10400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-10600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-108200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>5900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-7100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>7100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>5400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-1600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>31600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>13000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>17500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>22200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>17800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>17500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>22600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>44000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>7600</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E22" s="3">
         <v>9500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>9900</v>
-      </c>
-      <c r="F22" s="3">
-        <v>10300</v>
       </c>
       <c r="G22" s="3">
         <v>10300</v>
       </c>
       <c r="H22" s="3">
+        <v>10300</v>
+      </c>
+      <c r="I22" s="3">
         <v>10100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>10600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>9700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>7400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>3600</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
       <c r="N22" s="3">
         <v>0</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>12</v>
+      <c r="O22" s="3">
+        <v>0</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>12</v>
@@ -1752,112 +1791,118 @@
       <c r="R22" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="S22" s="3">
+      <c r="S22" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="T22" s="3">
         <v>3000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>1900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>3200</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="W22" s="3">
+      <c r="W22" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="X22" s="3">
         <v>3900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>9400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>15900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>3900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-4800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-39500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-5100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-8400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-8200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-4400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-100200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-32400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-130600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-6500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-19500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-4600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-9100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>24500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>8300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>4400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>10500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>6200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-5700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-5400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-5300</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1865,76 +1910,79 @@
         <v>600</v>
       </c>
       <c r="E24" s="3">
+        <v>600</v>
+      </c>
+      <c r="F24" s="3">
         <v>-7300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-11000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-29500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-5100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-2700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-100</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
       <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
         <v>900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2010,162 +2058,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-5400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-32100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-6000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-7700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-8800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-4700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-100000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-21500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-101000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-7700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-14400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-10800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>24500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>8000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>4500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>10500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>5300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-2800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-6700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-6000</v>
       </c>
-      <c r="AA26" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-4800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-24000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-4600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-6100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-7300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-3700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-139200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-13200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-72800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-7000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-10900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-4100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>24900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>3000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>10900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-5700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-12200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-7100</v>
       </c>
-      <c r="AA27" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2241,8 +2298,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2265,25 +2325,25 @@
         <v>0</v>
       </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>-59500</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-18700</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-35400</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-300</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-400</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
-      </c>
-      <c r="P29" s="3" t="s">
-        <v>12</v>
+      <c r="P29" s="3">
+        <v>0</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>12</v>
@@ -2291,8 +2351,8 @@
       <c r="R29" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="S29" s="3">
-        <v>0</v>
+      <c r="S29" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="T29" s="3">
         <v>0</v>
@@ -2300,26 +2360,29 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="W29" s="3">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="X29" s="3">
         <v>-200</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-11200</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="AA29" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2395,8 +2458,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2472,162 +2538,171 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E32" s="3">
         <v>600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="G32" s="3">
-        <v>-800</v>
-      </c>
       <c r="H32" s="3">
-        <v>-500</v>
+        <v>700</v>
       </c>
       <c r="I32" s="3">
         <v>-500</v>
       </c>
       <c r="J32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>9400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>3200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1400</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>3300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-2400</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-300</v>
       </c>
       <c r="T32" s="3">
         <v>-300</v>
       </c>
       <c r="U32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="V32" s="3">
         <v>1900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>2400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>600</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-500</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-4800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-24000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-4600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-6100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-7300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-3700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-139200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-31900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-108200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-7300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-11300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-4100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>24900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>3000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>10900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-7400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-23400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-7100</v>
       </c>
-      <c r="AA33" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2703,167 +2778,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-4800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-24000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-4600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-6100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-7300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-3700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-139200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-31900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-108200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-7300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-11300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-4100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>24900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>3000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>10900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-7400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-23400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-7100</v>
       </c>
-      <c r="AA35" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45563</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45472</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45381</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45108</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45017</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44835</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44744</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44653</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44471</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44380</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44289</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44100</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44009</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43918</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43645</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>42735</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>42462</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>42369</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2891,8 +2975,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2920,68 +3005,69 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>41600</v>
+      </c>
+      <c r="E41" s="3">
         <v>43100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>32000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>25200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>37000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>26800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>29400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>47100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>30200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>34400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>41000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>27400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>43900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>80900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>136100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>124200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>86800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>72500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>126200</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>12</v>
       </c>
@@ -2997,8 +3083,11 @@
       <c r="AA41" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3074,68 +3163,71 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>127500</v>
+      </c>
+      <c r="E43" s="3">
         <v>121900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>137300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>125500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>123000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>112900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>119600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>118500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>136600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>132200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>143000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>119300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>125000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>105400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>102000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>89500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>88400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>80900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>67400</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>12</v>
       </c>
@@ -3151,68 +3243,71 @@
       <c r="AA43" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>92500</v>
+      </c>
+      <c r="E44" s="3">
         <v>90000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>87600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>97000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>91300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>97600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>96300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>88000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>82900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>77000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>69100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>64700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>61700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>36600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>34000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>39800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>29100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>34700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>33800</v>
       </c>
-      <c r="V44" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="W44" s="3" t="s">
         <v>12</v>
       </c>
@@ -3228,20 +3323,23 @@
       <c r="AA44" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E45" s="3">
         <v>26700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>28400</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="G45" s="3" t="s">
         <v>12</v>
       </c>
@@ -3251,45 +3349,45 @@
       <c r="I45" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K45" s="3">
         <v>37900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>21100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>27600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>24100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>34000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>32400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>23200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>17900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>17200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>7500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>5000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>7100</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>12</v>
       </c>
@@ -3305,68 +3403,71 @@
       <c r="AA45" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>275600</v>
+      </c>
+      <c r="E46" s="3">
         <v>298700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>308900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>265900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>268000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>249500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>260600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>308700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>272600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>271100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>277200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>245400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>263100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>246100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>290100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>270700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>211800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>193100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>234400</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>12</v>
       </c>
@@ -3382,8 +3483,11 @@
       <c r="AA46" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3391,59 +3495,59 @@
         <v>1900</v>
       </c>
       <c r="E47" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F47" s="3">
         <v>2100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>3200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>3100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>6900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>6500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>5300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>13000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>78500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>28800</v>
-      </c>
-      <c r="O47" s="3">
-        <v>29300</v>
       </c>
       <c r="P47" s="3">
         <v>29300</v>
       </c>
       <c r="Q47" s="3">
+        <v>29300</v>
+      </c>
+      <c r="R47" s="3">
         <v>19500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>21200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>19400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>19900</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>3400</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="W47" s="3" t="s">
         <v>12</v>
       </c>
@@ -3459,68 +3563,71 @@
       <c r="AA47" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>33500</v>
+      </c>
+      <c r="E48" s="3">
         <v>39200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>42300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>47000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>50000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>54000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>57100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>52600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>44100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>42900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>43500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>43600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>40200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>27200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>26600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>26100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>21800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>19800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>18900</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>12</v>
       </c>
@@ -3536,68 +3643,71 @@
       <c r="AA48" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>412200</v>
+      </c>
+      <c r="E49" s="3">
         <v>422300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>432000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>478100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>489800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>500800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>512700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>523500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>647300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1071000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>809700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>829300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>842800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>301700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>310000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>324600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>241500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>246500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>252700</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="W49" s="3" t="s">
         <v>12</v>
       </c>
@@ -3613,8 +3723,11 @@
       <c r="AA49" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3690,8 +3803,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3767,8 +3883,11 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3793,32 +3912,32 @@
       <c r="J52" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K52" s="3">
+      <c r="K52" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L52" s="3">
         <v>406000</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
       <c r="M52" s="3">
         <v>0</v>
       </c>
       <c r="N52" s="3">
+        <v>0</v>
+      </c>
+      <c r="O52" s="3">
         <v>50000</v>
-      </c>
-      <c r="O52" s="3">
-        <v>50500</v>
       </c>
       <c r="P52" s="3">
         <v>50500</v>
       </c>
       <c r="Q52" s="3">
-        <v>500</v>
+        <v>50500</v>
       </c>
       <c r="R52" s="3">
         <v>500</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>12</v>
+      <c r="S52" s="3">
+        <v>500</v>
       </c>
       <c r="T52" s="3" t="s">
         <v>12</v>
@@ -3835,8 +3954,8 @@
       <c r="X52" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="Y52" s="3">
-        <v>0</v>
+      <c r="Y52" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="Z52" s="3">
         <v>0</v>
@@ -3844,8 +3963,11 @@
       <c r="AA52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3921,68 +4043,71 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>728000</v>
+      </c>
+      <c r="E54" s="3">
         <v>769500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>792200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>794200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>810900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>811100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>837000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>887400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1372600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1398000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1208800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1197100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1225900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>654800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>646600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>643100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>494500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>479300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>509400</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>12</v>
       </c>
@@ -3998,8 +4123,11 @@
       <c r="AA54" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4027,8 +4155,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4056,68 +4185,69 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>23700</v>
+      </c>
+      <c r="E57" s="3">
         <v>16800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>24400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>19100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>23000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>17600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>41400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>32800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>36700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>19100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>25700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>22500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>16900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>10900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>9900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>10300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>8800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>13600</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>12</v>
       </c>
@@ -4133,49 +4263,52 @@
       <c r="AA57" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>31300</v>
+      </c>
+      <c r="E58" s="3">
         <v>42500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>42400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>40600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>32700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>24300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>15300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>45600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>33100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>31300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>22500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>20300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>18000</v>
-      </c>
-      <c r="P58" s="3">
-        <v>15000</v>
       </c>
       <c r="Q58" s="3">
         <v>15000</v>
@@ -4187,14 +4320,14 @@
         <v>15000</v>
       </c>
       <c r="T58" s="3">
+        <v>15000</v>
+      </c>
+      <c r="U58" s="3">
         <v>16300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>15000</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="W58" s="3" t="s">
         <v>12</v>
       </c>
@@ -4210,68 +4343,71 @@
       <c r="AA58" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>89800</v>
+      </c>
+      <c r="E59" s="3">
         <v>97900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>115600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>68900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>64300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>74300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>74200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>72900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>351900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>238000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>150600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>128700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>145900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>134800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>133300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>123700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>103200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>86700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>68700</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>12</v>
       </c>
@@ -4287,68 +4423,71 @@
       <c r="AA59" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>210400</v>
+      </c>
+      <c r="E60" s="3">
         <v>211500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>231500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>173300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>175500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>160800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>179100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>196100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>304000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>288400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>198900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>171500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>180900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>160700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>158200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>149000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>122600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>111700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>97200</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>12</v>
       </c>
@@ -4364,68 +4503,71 @@
       <c r="AA60" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>324800</v>
+      </c>
+      <c r="E61" s="3">
         <v>362600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>363200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>375300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>388000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>397100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>387100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>424300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>385000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>393100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>351400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>348000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>339600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>162400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>166100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>169700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>173400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>177000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>229700</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
@@ -4441,68 +4583,71 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E62" s="3">
         <v>8600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>8500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>26900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>25100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>26700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>37500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>26300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>350700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>337400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>138300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>155700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>171600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>101200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>103000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>104000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>54300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>45200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>40700</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>12</v>
       </c>
@@ -4518,8 +4663,11 @@
       <c r="AA62" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4595,8 +4743,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4672,8 +4823,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4749,68 +4903,71 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>542400</v>
+      </c>
+      <c r="E66" s="3">
         <v>582700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>603100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>576800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>589800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>584600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>603600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>647000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1047400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1054600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>760800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>747400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>766900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>502300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>505100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>500700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>352200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>336100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>370200</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>12</v>
       </c>
@@ -4826,8 +4983,11 @@
       <c r="AA66" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4855,8 +5015,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4932,8 +5093,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5009,8 +5173,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5060,7 +5227,7 @@
         <v>0</v>
       </c>
       <c r="S70" s="3">
-        <v>168000</v>
+        <v>0</v>
       </c>
       <c r="T70" s="3">
         <v>168000</v>
@@ -5069,7 +5236,7 @@
         <v>168000</v>
       </c>
       <c r="V70" s="3">
-        <v>0</v>
+        <v>168000</v>
       </c>
       <c r="W70" s="3">
         <v>0</v>
@@ -5086,8 +5253,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5163,68 +5333,71 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-355100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-354900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-350100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-326100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-321500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-315400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-308100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-304500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-165300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-133400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-25100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-17900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-6600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-6200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-5200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-140700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-138400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-141500</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>12</v>
       </c>
@@ -5240,8 +5413,11 @@
       <c r="AA72" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5317,8 +5493,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5394,8 +5573,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5471,68 +5653,71 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>147900</v>
+      </c>
+      <c r="E76" s="3">
         <v>148700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>150900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>171300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>173600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>177500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>183200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>188500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>325200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>343400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>448000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>449800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>458900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>152500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>141600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>142400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-25800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-24800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-28800</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>12</v>
       </c>
@@ -5548,8 +5733,11 @@
       <c r="AA76" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5625,167 +5813,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45563</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45472</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45381</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45108</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45017</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44835</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44744</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44653</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44471</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44380</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44289</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44100</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44009</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43918</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43645</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>42735</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>42462</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>42369</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-4800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-24000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-4600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-6100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-7300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-3700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-139200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-31900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-108200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-7300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-11300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-4100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>24900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>3000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>10900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-7400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-23400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-7100</v>
       </c>
-      <c r="AA81" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5813,85 +6010,89 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>-18100</v>
+      </c>
+      <c r="E83" s="3">
         <v>13800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>14600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>16500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>-8500</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I83" s="3">
+      <c r="I83" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J83" s="3">
         <v>12400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>12500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>23200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>18800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>12400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>12500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>11700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>8500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>7500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>7200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>6900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>7300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>14500</v>
-      </c>
-      <c r="V83" s="3">
-        <v>7300</v>
       </c>
       <c r="W83" s="3">
         <v>7300</v>
       </c>
       <c r="X83" s="3">
+        <v>7300</v>
+      </c>
+      <c r="Y83" s="3">
         <v>15700</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="Z83" s="3">
+      <c r="Z83" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA83" s="3">
         <v>9100</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5967,8 +6168,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6044,8 +6248,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6121,8 +6328,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6198,8 +6408,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6275,85 +6488,91 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>19300</v>
+      </c>
+      <c r="E89" s="3">
         <v>10300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>15200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-6000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>10400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-8300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>10800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>5200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-21000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>13100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>10600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>17300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-18000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>25400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>20800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>25500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>17700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>21000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>8000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>37100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>2200</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6381,85 +6600,89 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-100</v>
+        <v>-600</v>
       </c>
       <c r="E91" s="3">
         <v>-100</v>
       </c>
       <c r="F91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G91" s="3">
         <v>-300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="Z91" s="3">
+      <c r="Z91" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-600</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6535,8 +6758,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6612,85 +6838,91 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-100</v>
+        <v>24100</v>
       </c>
       <c r="E94" s="3">
         <v>-100</v>
       </c>
       <c r="F94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G94" s="3">
         <v>-1000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>33500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-15100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-56300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-52000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-221300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-13200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-46600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-17800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-7300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-7900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-6600</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6718,8 +6950,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6744,8 +6977,8 @@
       <c r="J96" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -6795,8 +7028,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6872,8 +7108,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6949,8 +7188,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7026,235 +7268,247 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-42900</v>
+      </c>
+      <c r="E100" s="3">
         <v>400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-7800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-4200</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>8200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-62200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>27400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-5400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>50700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>7700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>9200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>176300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-6100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>107500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-9900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-57100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>37400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>48800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-11100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-9000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>5500</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>400</v>
+      </c>
+      <c r="E101" s="3">
         <v>-400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1100</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I101" s="3">
+      <c r="I101" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J101" s="3">
         <v>-200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1100</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-200</v>
       </c>
       <c r="M101" s="3">
         <v>-200</v>
       </c>
       <c r="N101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="O101" s="3">
         <v>-100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-200</v>
-      </c>
-      <c r="V101" s="3">
-        <v>-300</v>
       </c>
       <c r="W101" s="3">
         <v>-300</v>
       </c>
       <c r="X101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Y101" s="3">
         <v>300</v>
       </c>
-      <c r="Y101" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="Z101" s="3">
+      <c r="Z101" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA101" s="3">
         <v>200</v>
       </c>
-      <c r="AA101" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E102" s="3">
         <v>11100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>6800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-11800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>10100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-17700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>15300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-6600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-41700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-16600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-31700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-7200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>8600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>42600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>14400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-53800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>61700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>65800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>20900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-10200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>8000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1200</v>
       </c>
-      <c r="AA102" s="3" t="s">
+      <c r="AB102" s="3" t="s">
         <v>12</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BVS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BVS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="92">
   <si>
     <t>BVS</t>
   </si>
@@ -656,366 +656,379 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45563</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45472</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45381</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45108</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45017</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44835</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44744</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44653</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44471</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44380</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44289</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44100</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44009</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43918</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43645</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>42735</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>42462</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42369</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>123900</v>
+      </c>
+      <c r="E8" s="3">
         <v>153600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>139000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>151200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>129500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>135400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>120800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>137100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>119100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>125800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>128700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>140300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>117300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>130400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>108900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>109800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>81800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>98600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>85900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>136700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>78600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>97600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>160300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>274500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>65400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>71200</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>40800</v>
+      </c>
+      <c r="E9" s="3">
         <v>51000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>45400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>47600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>41100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>49100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>41900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>47900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>45100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>51600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>44100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>43700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>41600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>42600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>29800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>33500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>22200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>25100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>23400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>39100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>21400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>24100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>45100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>80400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>19200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>20200</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>83100</v>
+      </c>
+      <c r="E10" s="3">
         <v>102700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>93600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>103600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>88400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>86300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>78900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>89100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>73900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>74200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>84600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>96600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>75700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>87800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>79100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>76300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>59600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>73500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>62500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>97600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>57200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>73500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>115200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>194100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>46200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>51000</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1044,88 +1057,92 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E12" s="3">
         <v>3200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>3800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>4000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>2600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>3300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>3000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>3400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>5900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>4600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>6400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>6900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>7100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>6200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>4800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>2900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>3600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>4700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>2100</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>3100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>5100</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>7900</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>3700</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1204,132 +1221,138 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>100</v>
+      </c>
+      <c r="E14" s="3">
         <v>3100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>2600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>44700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>77700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>4600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>314500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>3900</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>5700</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="U14" s="3">
         <v>900</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-2300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>3500</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="X14" s="3">
+      <c r="X14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y14" s="3">
         <v>3300</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>500</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>8800</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>200</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E15" s="3">
         <v>1800</v>
-      </c>
-      <c r="E15" s="3">
-        <v>2100</v>
       </c>
       <c r="F15" s="3">
         <v>2100</v>
       </c>
       <c r="G15" s="3">
+        <v>2100</v>
+      </c>
+      <c r="H15" s="3">
         <v>1800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2100</v>
-      </c>
-      <c r="I15" s="3">
-        <v>2300</v>
       </c>
       <c r="J15" s="3">
         <v>2300</v>
       </c>
       <c r="K15" s="3">
+        <v>2300</v>
+      </c>
+      <c r="L15" s="3">
         <v>2100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>2700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>3300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>2700</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>1900</v>
       </c>
       <c r="R15" s="3">
         <v>1900</v>
@@ -1338,34 +1361,37 @@
         <v>1900</v>
       </c>
       <c r="T15" s="3">
+        <v>1900</v>
+      </c>
+      <c r="U15" s="3">
         <v>2100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>1700</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>3600</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>1800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>2100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>3800</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>11000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>2800</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1391,168 +1417,175 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>118900</v>
+      </c>
+      <c r="E17" s="3">
         <v>142500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>132300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>135900</v>
       </c>
-      <c r="G17" s="3">
-        <v>123800</v>
-      </c>
       <c r="H17" s="3">
+        <v>124200</v>
+      </c>
+      <c r="I17" s="3">
         <v>132800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>117100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>128500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>131900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>141500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>255500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>143600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>138700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>133600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>112100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>115600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>59800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>92700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>75900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>127200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>65700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>86800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>153500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>263600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>67400</v>
       </c>
-      <c r="AB17" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E18" s="3">
         <v>11100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>6600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>15300</v>
       </c>
-      <c r="G18" s="3">
-        <v>5600</v>
-      </c>
       <c r="H18" s="3">
+        <v>5200</v>
+      </c>
+      <c r="I18" s="3">
         <v>2600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>8600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-12800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-15700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-126800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-3300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-21400</v>
-      </c>
-      <c r="P18" s="3">
-        <v>-3200</v>
       </c>
       <c r="Q18" s="3">
         <v>-3200</v>
       </c>
       <c r="R18" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="S18" s="3">
         <v>-5800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>22000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>5900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>10000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>9500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>12900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>10800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>6900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>10900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC18" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1581,209 +1614,216 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>800</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-700</v>
-      </c>
-      <c r="I20" s="3">
-        <v>500</v>
       </c>
       <c r="J20" s="3">
         <v>500</v>
       </c>
       <c r="K20" s="3">
+        <v>500</v>
+      </c>
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-9400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-3200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>-3300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>2400</v>
-      </c>
-      <c r="T20" s="3">
-        <v>300</v>
       </c>
       <c r="U20" s="3">
         <v>300</v>
       </c>
       <c r="V20" s="3">
+        <v>300</v>
+      </c>
+      <c r="W20" s="3">
         <v>-1900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-2400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-600</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>500</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E21" s="3">
         <v>14100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>9300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>17200</v>
       </c>
-      <c r="G21" s="3">
-        <v>7300</v>
-      </c>
       <c r="H21" s="3">
+        <v>6900</v>
+      </c>
+      <c r="I21" s="3">
         <v>5400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>5500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>10400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-10600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-108200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>5900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-7100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>7100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>5400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-1600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>31600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>13000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>17500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>22200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>17800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>17500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>22600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>44000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>7600</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E22" s="3">
         <v>9000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>9500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>9900</v>
-      </c>
-      <c r="G22" s="3">
-        <v>10300</v>
       </c>
       <c r="H22" s="3">
         <v>10300</v>
       </c>
       <c r="I22" s="3">
+        <v>10300</v>
+      </c>
+      <c r="J22" s="3">
         <v>10100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>10600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>9700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>7400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>3600</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>12</v>
+      <c r="P22" s="3">
+        <v>0</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>12</v>
@@ -1794,195 +1834,204 @@
       <c r="S22" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="T22" s="3">
+      <c r="T22" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="U22" s="3">
         <v>3000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>1900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>3200</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="X22" s="3">
+      <c r="X22" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y22" s="3">
         <v>3900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>9400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>15900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>3900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E23" s="3">
         <v>200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-4800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-39500</v>
       </c>
-      <c r="G23" s="3">
-        <v>-5100</v>
-      </c>
       <c r="H23" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="I23" s="3">
         <v>-8400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-8200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-4400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-100200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-32400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-130600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-6500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-19500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-3200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-9100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>24500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>3100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>8300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>4400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>10500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>6200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-5700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-5400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-5300</v>
       </c>
     </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>600</v>
+        <v>-100</v>
       </c>
       <c r="E24" s="3">
         <v>600</v>
       </c>
       <c r="F24" s="3">
+        <v>600</v>
+      </c>
+      <c r="G24" s="3">
         <v>-7300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-11000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-29500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-5100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-100</v>
       </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
       <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
         <v>900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2061,168 +2110,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-5400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-32100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="J26" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="K26" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="L26" s="3">
+        <v>-100000</v>
+      </c>
+      <c r="M26" s="3">
+        <v>-21500</v>
+      </c>
+      <c r="N26" s="3">
+        <v>-101000</v>
+      </c>
+      <c r="O26" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="P26" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="R26" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="S26" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="T26" s="3">
+        <v>24500</v>
+      </c>
+      <c r="U26" s="3">
+        <v>2300</v>
+      </c>
+      <c r="V26" s="3">
+        <v>8000</v>
+      </c>
+      <c r="W26" s="3">
+        <v>4500</v>
+      </c>
+      <c r="X26" s="3">
+        <v>10500</v>
+      </c>
+      <c r="Y26" s="3">
+        <v>5300</v>
+      </c>
+      <c r="Z26" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="AA26" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="AB26" s="3">
         <v>-6000</v>
       </c>
-      <c r="H26" s="3">
-        <v>-7700</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-8800</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-4700</v>
-      </c>
-      <c r="K26" s="3">
-        <v>-100000</v>
-      </c>
-      <c r="L26" s="3">
-        <v>-21500</v>
-      </c>
-      <c r="M26" s="3">
-        <v>-101000</v>
-      </c>
-      <c r="N26" s="3">
-        <v>-7700</v>
-      </c>
-      <c r="O26" s="3">
-        <v>-14400</v>
-      </c>
-      <c r="P26" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="R26" s="3">
-        <v>-10800</v>
-      </c>
-      <c r="S26" s="3">
-        <v>24500</v>
-      </c>
-      <c r="T26" s="3">
-        <v>2300</v>
-      </c>
-      <c r="U26" s="3">
-        <v>8000</v>
-      </c>
-      <c r="V26" s="3">
-        <v>4500</v>
-      </c>
-      <c r="W26" s="3">
-        <v>10500</v>
-      </c>
-      <c r="X26" s="3">
-        <v>5300</v>
-      </c>
-      <c r="Y26" s="3">
-        <v>-2800</v>
-      </c>
-      <c r="Z26" s="3">
-        <v>-6700</v>
-      </c>
-      <c r="AA26" s="3">
-        <v>-6000</v>
-      </c>
-      <c r="AB26" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-4800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-24000</v>
       </c>
-      <c r="G27" s="3">
-        <v>-4600</v>
-      </c>
       <c r="H27" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="I27" s="3">
         <v>-6100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-7300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-3700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-139200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-13200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-72800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-7000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-10900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-4100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>24900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>3000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>10900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-5700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-12200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-7100</v>
       </c>
-      <c r="AB27" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2301,8 +2359,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2328,25 +2389,25 @@
         <v>0</v>
       </c>
       <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>-59500</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-18700</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-35400</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-300</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-400</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="3" t="s">
-        <v>12</v>
+      <c r="Q29" s="3">
+        <v>0</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>12</v>
@@ -2354,8 +2415,8 @@
       <c r="S29" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="T29" s="3">
-        <v>0</v>
+      <c r="T29" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="U29" s="3">
         <v>0</v>
@@ -2363,26 +2424,29 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="X29" s="3">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y29" s="3">
         <v>-200</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-11200</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="AB29" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2461,8 +2525,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2541,168 +2608,177 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E32" s="3">
         <v>1200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>700</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-500</v>
       </c>
       <c r="J32" s="3">
         <v>-500</v>
       </c>
       <c r="K32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>9400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>3200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1400</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>3300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-2400</v>
-      </c>
-      <c r="T32" s="3">
-        <v>-300</v>
       </c>
       <c r="U32" s="3">
         <v>-300</v>
       </c>
       <c r="V32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="W32" s="3">
         <v>1900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>2400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>600</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
       <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-500</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-4800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-24000</v>
       </c>
-      <c r="G33" s="3">
-        <v>-4600</v>
-      </c>
       <c r="H33" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="I33" s="3">
         <v>-6100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-7300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-3700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-139200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-31900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-108200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-7300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-11300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-4100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>24900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>3000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>10900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-7400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-23400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-7100</v>
       </c>
-      <c r="AB33" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2781,173 +2857,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-4800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-24000</v>
       </c>
-      <c r="G35" s="3">
-        <v>-4600</v>
-      </c>
       <c r="H35" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="I35" s="3">
         <v>-6100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-7300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-3700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-139200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-31900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-108200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-7300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-11300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-4100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>24900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>3000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>10900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-7400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-23400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-7100</v>
       </c>
-      <c r="AB35" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45563</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45472</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45381</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45108</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45017</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44835</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44744</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44653</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44471</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44380</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44289</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44100</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44009</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43918</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43645</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>42735</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>42462</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42369</v>
       </c>
     </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2976,8 +3061,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3006,71 +3092,72 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>22800</v>
+      </c>
+      <c r="E41" s="3">
         <v>41600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>43100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>32000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>25200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>37000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>26800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>29400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>47100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>30200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>34400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>41000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>27400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>43900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>80900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>136100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>124200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>86800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>72500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>126200</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>12</v>
       </c>
@@ -3086,8 +3173,11 @@
       <c r="AB41" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3166,71 +3256,74 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>118100</v>
+      </c>
+      <c r="E43" s="3">
         <v>127500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>121900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>137300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>125500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>123000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>112900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>119600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>118500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>136600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>132200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>143000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>119300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>125000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>105400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>102000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>89500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>88400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>80900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>67400</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>12</v>
       </c>
@@ -3246,71 +3339,74 @@
       <c r="AB43" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>94000</v>
+      </c>
+      <c r="E44" s="3">
         <v>92500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>90000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>87600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>97000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>91300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>97600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>96300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>88000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>82900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>77000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>69100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>64700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>61700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>36600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>34000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>39800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>29100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>34700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>33800</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="X44" s="3" t="s">
         <v>12</v>
       </c>
@@ -3326,23 +3422,26 @@
       <c r="AB44" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F45" s="3">
         <v>26700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>28400</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="H45" s="3" t="s">
         <v>12</v>
       </c>
@@ -3352,45 +3451,45 @@
       <c r="J45" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L45" s="3">
         <v>37900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>21100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>27600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>24100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>34000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>32400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>23200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>17900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>17200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>7500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>5000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>7100</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>12</v>
       </c>
@@ -3406,71 +3505,74 @@
       <c r="AB45" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>249400</v>
+      </c>
+      <c r="E46" s="3">
         <v>275600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>298700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>308900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>265900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>268000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>249500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>260600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>308700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>272600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>271100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>277200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>245400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>263100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>246100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>290100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>270700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>211800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>193100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>234400</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>12</v>
       </c>
@@ -3486,71 +3588,74 @@
       <c r="AB46" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1900</v>
+        <v>1800</v>
       </c>
       <c r="E47" s="3">
         <v>1900</v>
       </c>
       <c r="F47" s="3">
+        <v>1900</v>
+      </c>
+      <c r="G47" s="3">
         <v>2100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>3200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>3100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>6900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>6500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>5300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>13000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>78500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>28800</v>
-      </c>
-      <c r="P47" s="3">
-        <v>29300</v>
       </c>
       <c r="Q47" s="3">
         <v>29300</v>
       </c>
       <c r="R47" s="3">
+        <v>29300</v>
+      </c>
+      <c r="S47" s="3">
         <v>19500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>21200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>19400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>19900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>3400</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="X47" s="3" t="s">
         <v>12</v>
       </c>
@@ -3566,71 +3671,74 @@
       <c r="AB47" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>32400</v>
+      </c>
+      <c r="E48" s="3">
         <v>33500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>39200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>42300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>47000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>50000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>54000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>57100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>52600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>44100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>42900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>43500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>43600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>40200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>27200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>26600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>26100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>21800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>19800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>18900</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>12</v>
       </c>
@@ -3646,71 +3754,74 @@
       <c r="AB48" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>403200</v>
+      </c>
+      <c r="E49" s="3">
         <v>412200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>422300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>432000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>478100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>489800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>500800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>512700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>523500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>647300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1071000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>809700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>829300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>842800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>301700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>310000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>324600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>241500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>246500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>252700</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="X49" s="3" t="s">
         <v>12</v>
       </c>
@@ -3726,8 +3837,11 @@
       <c r="AB49" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3806,8 +3920,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3886,8 +4003,11 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3915,32 +4035,32 @@
       <c r="K52" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L52" s="3">
+      <c r="L52" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M52" s="3">
         <v>406000</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
-      </c>
       <c r="N52" s="3">
         <v>0</v>
       </c>
       <c r="O52" s="3">
+        <v>0</v>
+      </c>
+      <c r="P52" s="3">
         <v>50000</v>
-      </c>
-      <c r="P52" s="3">
-        <v>50500</v>
       </c>
       <c r="Q52" s="3">
         <v>50500</v>
       </c>
       <c r="R52" s="3">
-        <v>500</v>
+        <v>50500</v>
       </c>
       <c r="S52" s="3">
         <v>500</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>12</v>
+      <c r="T52" s="3">
+        <v>500</v>
       </c>
       <c r="U52" s="3" t="s">
         <v>12</v>
@@ -3957,8 +4077,8 @@
       <c r="Y52" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="Z52" s="3">
-        <v>0</v>
+      <c r="Z52" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="AA52" s="3">
         <v>0</v>
@@ -3966,8 +4086,11 @@
       <c r="AB52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4046,71 +4169,74 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>691400</v>
+      </c>
+      <c r="E54" s="3">
         <v>728000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>769500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>792200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>794200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>810900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>811100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>837000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>887400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1372600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1398000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1208800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1197100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1225900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>654800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>646600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>643100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>494500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>479300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>509400</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>12</v>
       </c>
@@ -4126,8 +4252,11 @@
       <c r="AB54" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4156,8 +4285,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4186,71 +4316,72 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>19200</v>
+      </c>
+      <c r="E57" s="3">
         <v>23700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>16800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>24400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>19100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>23000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>17600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>41400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>32800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>36700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>19100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>25700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>22500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>16900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>10900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>9900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>10300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>8800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>13600</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>12</v>
       </c>
@@ -4266,52 +4397,55 @@
       <c r="AB57" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>41700</v>
+      </c>
+      <c r="E58" s="3">
         <v>31300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>42500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>42400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>40600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>32700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>24300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>15300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>45600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>33100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>31300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>22500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>20300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>18000</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>15000</v>
       </c>
       <c r="R58" s="3">
         <v>15000</v>
@@ -4323,14 +4457,14 @@
         <v>15000</v>
       </c>
       <c r="U58" s="3">
+        <v>15000</v>
+      </c>
+      <c r="V58" s="3">
         <v>16300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>15000</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>12</v>
       </c>
@@ -4346,71 +4480,74 @@
       <c r="AB58" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>77900</v>
+      </c>
+      <c r="E59" s="3">
         <v>89800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>97900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>115600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>68900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>64300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>74300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>74200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>72900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>351900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>238000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>150600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>128700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>145900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>134800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>133300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>123700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>103200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>86700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>68700</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>12</v>
       </c>
@@ -4426,71 +4563,74 @@
       <c r="AB59" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>174800</v>
+      </c>
+      <c r="E60" s="3">
         <v>210400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>211500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>231500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>173300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>175500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>160800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>179100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>196100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>304000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>288400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>198900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>171500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>180900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>160700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>158200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>149000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>122600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>111700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>97200</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>12</v>
       </c>
@@ -4506,71 +4646,74 @@
       <c r="AB60" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>324400</v>
+      </c>
+      <c r="E61" s="3">
         <v>324800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>362600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>363200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>375300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>388000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>397100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>387100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>424300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>385000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>393100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>351400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>348000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>339600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>162400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>166100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>169700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>173400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>177000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>229700</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
@@ -4586,71 +4729,74 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E62" s="3">
         <v>6600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>8600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>8500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>26900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>25100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>26700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>37500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>26300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>350700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>337400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>138300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>155700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>171600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>101200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>103000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>104000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>54300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>45200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>40700</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>12</v>
       </c>
@@ -4666,8 +4812,11 @@
       <c r="AB62" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4746,8 +4895,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4826,8 +4978,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4906,71 +5061,74 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>505900</v>
+      </c>
+      <c r="E66" s="3">
         <v>542400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>582700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>603100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>576800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>589800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>584600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>603600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>647000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1047400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1054600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>760800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>747400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>766900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>502300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>505100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>500700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>352200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>336100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>370200</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>12</v>
       </c>
@@ -4986,8 +5144,11 @@
       <c r="AB66" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5016,8 +5177,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5096,8 +5258,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5176,8 +5341,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5230,7 +5398,7 @@
         <v>0</v>
       </c>
       <c r="T70" s="3">
-        <v>168000</v>
+        <v>0</v>
       </c>
       <c r="U70" s="3">
         <v>168000</v>
@@ -5239,7 +5407,7 @@
         <v>168000</v>
       </c>
       <c r="W70" s="3">
-        <v>0</v>
+        <v>168000</v>
       </c>
       <c r="X70" s="3">
         <v>0</v>
@@ -5256,8 +5424,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5336,71 +5507,74 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-360300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-355100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-354900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-350100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-326100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-321500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-315400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-308100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-304500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-165300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-133400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-25100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-17900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-6600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-6200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-5200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-1000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-140700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-138400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-141500</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>12</v>
       </c>
@@ -5416,8 +5590,11 @@
       <c r="AB72" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5496,8 +5673,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5576,8 +5756,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5656,71 +5839,74 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>148100</v>
+      </c>
+      <c r="E76" s="3">
         <v>147900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>148700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>150900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>171300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>173600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>177500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>183200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>188500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>325200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>343400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>448000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>449800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>458900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>152500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>141600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>142400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-25800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-24800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-28800</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>12</v>
       </c>
@@ -5736,8 +5922,11 @@
       <c r="AB76" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5816,173 +6005,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45563</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45472</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45381</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45108</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45017</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44835</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44744</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44653</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44471</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44380</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44289</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44100</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44009</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43918</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43645</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>42735</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>42462</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42369</v>
       </c>
     </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-4800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-24000</v>
       </c>
-      <c r="G81" s="3">
-        <v>-4600</v>
-      </c>
       <c r="H81" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="I81" s="3">
         <v>-6100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-7300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-3700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-139200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-31900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-108200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-7300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-11300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-4100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>24900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>3000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>10900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-7400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-23400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-7100</v>
       </c>
-      <c r="AB81" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6011,88 +6209,92 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E83" s="3">
         <v>-18100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>13800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>14600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>16500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>-8500</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J83" s="3">
+      <c r="J83" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K83" s="3">
         <v>12400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>12500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>23200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>18800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>12400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>12500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>11700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>8500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>7500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>7200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>6900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>7300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>14500</v>
-      </c>
-      <c r="W83" s="3">
-        <v>7300</v>
       </c>
       <c r="X83" s="3">
         <v>7300</v>
       </c>
       <c r="Y83" s="3">
+        <v>7300</v>
+      </c>
+      <c r="Z83" s="3">
         <v>15700</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="AA83" s="3">
+      <c r="AA83" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB83" s="3">
         <v>9100</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6171,8 +6373,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6251,8 +6456,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6331,8 +6539,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6411,8 +6622,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6491,88 +6705,94 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-19300</v>
+      </c>
+      <c r="E89" s="3">
         <v>19300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>10300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>15200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-6000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>10400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-8300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>10800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>5200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-21000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>13100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>10600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>17300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-18000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>25400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>20800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>25500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>17700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>21000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>8000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>37100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>2200</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6601,88 +6821,92 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-600</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-100</v>
       </c>
       <c r="F91" s="3">
         <v>-100</v>
       </c>
       <c r="G91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H91" s="3">
         <v>-300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="AA91" s="3">
+      <c r="AA91" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-600</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6761,8 +6985,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6841,88 +7068,94 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E94" s="3">
         <v>24100</v>
-      </c>
-      <c r="E94" s="3">
-        <v>-100</v>
       </c>
       <c r="F94" s="3">
         <v>-100</v>
       </c>
       <c r="G94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H94" s="3">
         <v>-1000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>33500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-15100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-56300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-52000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-221300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-13200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-46600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-17800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-7300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-7900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-6600</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6951,8 +7184,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6980,8 +7214,8 @@
       <c r="K96" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -7031,8 +7265,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7111,8 +7348,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7191,8 +7431,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7271,244 +7514,256 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-42900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-7800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-4200</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>8200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-62200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>27400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-5400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>50700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>7700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>9200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>176300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-4300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-6100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>107500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-9900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-57100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>37400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>48800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-11100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-9000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>5500</v>
       </c>
-      <c r="AB100" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E101" s="3">
         <v>400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1100</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J101" s="3">
+      <c r="J101" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K101" s="3">
         <v>-200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1100</v>
-      </c>
-      <c r="M101" s="3">
-        <v>-200</v>
       </c>
       <c r="N101" s="3">
         <v>-200</v>
       </c>
       <c r="O101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="P101" s="3">
         <v>-100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-200</v>
-      </c>
-      <c r="W101" s="3">
-        <v>-300</v>
       </c>
       <c r="X101" s="3">
         <v>-300</v>
       </c>
       <c r="Y101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Z101" s="3">
         <v>300</v>
       </c>
-      <c r="Z101" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="AA101" s="3">
+      <c r="AA101" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB101" s="3">
         <v>200</v>
       </c>
-      <c r="AB101" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-18800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>11100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>6800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-11800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>10100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-17700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>15300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-6600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-41700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-16600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-31700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-7200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>8600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>42600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>14400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-53800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>61700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>65800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>20900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-10200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>8000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1200</v>
       </c>
-      <c r="AB102" s="3" t="s">
+      <c r="AC102" s="3" t="s">
         <v>12</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BVS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BVS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="92">
   <si>
     <t>BVS</t>
   </si>
@@ -656,379 +656,392 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45836</v>
+      </c>
+      <c r="E7" s="2">
         <v>45745</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45563</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45472</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45381</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45108</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45017</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44835</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44744</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44653</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44471</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44380</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44289</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44100</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44009</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43918</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43645</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>42735</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42462</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42369</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>147700</v>
+      </c>
+      <c r="E8" s="3">
         <v>123900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>153600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>139000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>151200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>129500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>135400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>120800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>137100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>119100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>125800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>128700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>140300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>117300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>130400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>108900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>109800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>81800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>98600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>85900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>136700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>78600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>97600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>160300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>274500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>65400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>71200</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>45600</v>
+      </c>
+      <c r="E9" s="3">
         <v>40800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>51000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>45400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>47600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>41100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>49100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>41900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>47900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>45100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>51600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>44100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>43700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>41600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>42600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>29800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>33500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>22200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>25100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>23400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>39100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>21400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>24100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>45100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>80400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>19200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>20200</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>102100</v>
+      </c>
+      <c r="E10" s="3">
         <v>83100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>102700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>93600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>103600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>88400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>86300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>78900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>89100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>73900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>74200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>84600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>96600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>75700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>87800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>79100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>76300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>59600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>73500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>62500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>97600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>57200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>73500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>115200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>194100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>46200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>51000</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1058,91 +1071,95 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E12" s="3">
         <v>3000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>3200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>3800</v>
       </c>
-      <c r="G12" s="3">
-        <v>4000</v>
-      </c>
       <c r="H12" s="3">
+        <v>4200</v>
+      </c>
+      <c r="I12" s="3">
         <v>2600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>3300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>3000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>5900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>4600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>6400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>6900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>7100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>6200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>4800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>2900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>3600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>4700</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>2100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>3100</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>5100</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>7900</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>3700</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1224,138 +1241,144 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>3100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>44700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>77700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>4600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>314500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>3900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>5700</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="V14" s="3">
         <v>900</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-2300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>3500</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="Y14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z14" s="3">
         <v>3300</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>500</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>8800</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>200</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E15" s="3">
         <v>1600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1800</v>
-      </c>
-      <c r="F15" s="3">
-        <v>2100</v>
       </c>
       <c r="G15" s="3">
         <v>2100</v>
       </c>
       <c r="H15" s="3">
+        <v>2100</v>
+      </c>
+      <c r="I15" s="3">
         <v>1800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2100</v>
-      </c>
-      <c r="J15" s="3">
-        <v>2300</v>
       </c>
       <c r="K15" s="3">
         <v>2300</v>
       </c>
       <c r="L15" s="3">
+        <v>2300</v>
+      </c>
+      <c r="M15" s="3">
         <v>2100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>2300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>2700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>3300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>2700</v>
-      </c>
-      <c r="R15" s="3">
-        <v>1900</v>
       </c>
       <c r="S15" s="3">
         <v>1900</v>
@@ -1364,34 +1387,37 @@
         <v>1900</v>
       </c>
       <c r="U15" s="3">
+        <v>1900</v>
+      </c>
+      <c r="V15" s="3">
         <v>2100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>1700</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>3600</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>1800</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>2100</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>3800</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>11000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>2800</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1418,174 +1444,181 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>129300</v>
+      </c>
+      <c r="E17" s="3">
         <v>118900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>142500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>132300</v>
       </c>
-      <c r="G17" s="3">
-        <v>135900</v>
-      </c>
       <c r="H17" s="3">
+        <v>138000</v>
+      </c>
+      <c r="I17" s="3">
         <v>124200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>132800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>117100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>128500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>131900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>141500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>255500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>143600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>138700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>133600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>112100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>115600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>59800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>92700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>75900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>127200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>65700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>86800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>153500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>263600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>67400</v>
       </c>
-      <c r="AC17" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD17" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>18400</v>
+      </c>
+      <c r="E18" s="3">
         <v>5000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>11100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>6600</v>
       </c>
-      <c r="G18" s="3">
-        <v>15300</v>
-      </c>
       <c r="H18" s="3">
+        <v>13200</v>
+      </c>
+      <c r="I18" s="3">
         <v>5200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>8600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-12800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-15700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-126800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-3300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-21400</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>-3200</v>
       </c>
       <c r="R18" s="3">
         <v>-3200</v>
       </c>
       <c r="S18" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="T18" s="3">
         <v>-5800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>22000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>5900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>10000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>9500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>12900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>10800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>6900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>10900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-2000</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD18" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1615,174 +1648,181 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>600</v>
+      </c>
+      <c r="E20" s="3">
         <v>800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-700</v>
-      </c>
-      <c r="J20" s="3">
-        <v>500</v>
       </c>
       <c r="K20" s="3">
         <v>500</v>
       </c>
       <c r="L20" s="3">
+        <v>500</v>
+      </c>
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-9400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-3200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1400</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>-3300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>2400</v>
-      </c>
-      <c r="U20" s="3">
-        <v>300</v>
       </c>
       <c r="V20" s="3">
         <v>300</v>
       </c>
       <c r="W20" s="3">
+        <v>300</v>
+      </c>
+      <c r="X20" s="3">
         <v>-1900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-600</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>500</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>19300</v>
+      </c>
+      <c r="E21" s="3">
         <v>5800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>14100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>9300</v>
       </c>
-      <c r="G21" s="3">
-        <v>17200</v>
-      </c>
       <c r="H21" s="3">
+        <v>15100</v>
+      </c>
+      <c r="I21" s="3">
         <v>6900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>5400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>5500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>10400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-10600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-108200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>5900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>7100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>5400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-1600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>31600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>13000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>17500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>22200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>17800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>17500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>22600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>44000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>7600</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1790,43 +1830,43 @@
         <v>7500</v>
       </c>
       <c r="E22" s="3">
+        <v>7500</v>
+      </c>
+      <c r="F22" s="3">
         <v>9000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>9500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>9900</v>
-      </c>
-      <c r="H22" s="3">
-        <v>10300</v>
       </c>
       <c r="I22" s="3">
         <v>10300</v>
       </c>
       <c r="J22" s="3">
+        <v>10300</v>
+      </c>
+      <c r="K22" s="3">
         <v>10100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>10600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>9700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>7400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>3600</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>12</v>
+      <c r="Q22" s="3">
+        <v>0</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>12</v>
@@ -1837,201 +1877,210 @@
       <c r="T22" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="U22" s="3">
+      <c r="U22" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="V22" s="3">
         <v>3000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>1900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>3200</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="Y22" s="3">
+      <c r="Y22" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z22" s="3">
         <v>3900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>9400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>15900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>3900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-3400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-4800</v>
       </c>
-      <c r="G23" s="3">
-        <v>-39500</v>
-      </c>
       <c r="H23" s="3">
+        <v>-41600</v>
+      </c>
+      <c r="I23" s="3">
         <v>-5500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-8400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-8200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-4400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-100200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-32400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-130600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-6500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-19500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-4600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-3200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-9100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>24500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>3100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>8300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>4400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>10500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>6200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-5700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-5400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-5300</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-100</v>
-      </c>
-      <c r="E24" s="3">
-        <v>600</v>
       </c>
       <c r="F24" s="3">
         <v>600</v>
       </c>
       <c r="G24" s="3">
+        <v>600</v>
+      </c>
+      <c r="H24" s="3">
         <v>-7300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-11000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-29500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-2700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-100</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
-      </c>
       <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
         <v>900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2113,174 +2162,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-3300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-5400</v>
       </c>
-      <c r="G26" s="3">
-        <v>-32100</v>
-      </c>
       <c r="H26" s="3">
+        <v>-34200</v>
+      </c>
+      <c r="I26" s="3">
         <v>-6400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-7700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-8800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-4700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-100000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-21500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-101000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-7700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-14400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-10800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>24500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>8000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>4500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>10500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>5300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-6700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-6000</v>
       </c>
-      <c r="AC26" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD26" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-4800</v>
       </c>
-      <c r="G27" s="3">
-        <v>-24000</v>
-      </c>
       <c r="H27" s="3">
+        <v>-25700</v>
+      </c>
+      <c r="I27" s="3">
         <v>-4900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-6100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-7300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-3700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-139200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-13200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-72800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-7000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-10900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-4100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>24900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>3000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>10900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>2700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-5700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-12200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-7100</v>
       </c>
-      <c r="AC27" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD27" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2362,8 +2420,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2392,25 +2453,25 @@
         <v>0</v>
       </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>-59500</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-18700</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-35400</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-300</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-400</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
-      <c r="R29" s="3" t="s">
-        <v>12</v>
+      <c r="R29" s="3">
+        <v>0</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>12</v>
@@ -2418,8 +2479,8 @@
       <c r="T29" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
+      <c r="U29" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="V29" s="3">
         <v>0</v>
@@ -2427,26 +2488,29 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="Y29" s="3">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z29" s="3">
         <v>-200</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-11200</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="AC29" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2528,8 +2592,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2611,174 +2678,183 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>700</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-500</v>
       </c>
       <c r="K32" s="3">
         <v>-500</v>
       </c>
       <c r="L32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="M32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>9400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>3200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1400</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>3300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-2400</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-300</v>
       </c>
       <c r="V32" s="3">
         <v>-300</v>
       </c>
       <c r="W32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="X32" s="3">
         <v>1900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>2400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>600</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
         <v>700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-500</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-4800</v>
       </c>
-      <c r="G33" s="3">
-        <v>-24000</v>
-      </c>
       <c r="H33" s="3">
+        <v>-25700</v>
+      </c>
+      <c r="I33" s="3">
         <v>-4900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-6100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-7300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-3700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-139200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-31900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-108200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-7300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-11300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-4100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>24900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>3000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>10900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>2500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-7400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-23400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-7100</v>
       </c>
-      <c r="AC33" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD33" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2860,179 +2936,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-4800</v>
       </c>
-      <c r="G35" s="3">
-        <v>-24000</v>
-      </c>
       <c r="H35" s="3">
+        <v>-25700</v>
+      </c>
+      <c r="I35" s="3">
         <v>-4900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-6100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-7300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-3700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-139200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-31900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-108200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-7300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-11300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-4100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>24900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>3000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>10900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>2500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-7400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-23400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-7100</v>
       </c>
-      <c r="AC35" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD35" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45836</v>
+      </c>
+      <c r="E38" s="2">
         <v>45745</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45563</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45472</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45381</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45108</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45017</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44835</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44744</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44653</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44471</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44380</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44289</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44100</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44009</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43918</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43645</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>42735</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42462</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42369</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3062,8 +3147,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3093,74 +3179,75 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>32900</v>
+      </c>
+      <c r="E41" s="3">
         <v>22800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>41600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>43100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>32000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>25200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>37000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>26800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>29400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>47100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>30200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>34400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>41000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>27400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>43900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>80900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>136100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>124200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>86800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>72500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>126200</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>12</v>
       </c>
@@ -3176,8 +3263,11 @@
       <c r="AC41" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3259,74 +3349,77 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>132400</v>
+      </c>
+      <c r="E43" s="3">
         <v>118100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>127500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>121900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>137300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>125500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>123000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>112900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>119600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>118500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>136600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>132200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>143000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>119300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>125000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>105400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>102000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>89500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>88400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>80900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>67400</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="Y43" s="3" t="s">
         <v>12</v>
       </c>
@@ -3342,74 +3435,77 @@
       <c r="AC43" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>96500</v>
+      </c>
+      <c r="E44" s="3">
         <v>94000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>92500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>90000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>87600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>97000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>91300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>97600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>96300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>88000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>82900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>77000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>69100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>64700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>61700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>36600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>34000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>39800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>29100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>34700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>33800</v>
       </c>
-      <c r="X44" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="Y44" s="3" t="s">
         <v>12</v>
       </c>
@@ -3425,8 +3521,11 @@
       <c r="AC44" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3436,15 +3535,15 @@
       <c r="E45" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G45" s="3">
         <v>26700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>28400</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>12</v>
       </c>
@@ -3454,45 +3553,45 @@
       <c r="K45" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M45" s="3">
         <v>37900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>21100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>27600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>24100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>34000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>32400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>23200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>17900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>17200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>7500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>5000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>7100</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>12</v>
       </c>
@@ -3508,74 +3607,77 @@
       <c r="AC45" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>275200</v>
+      </c>
+      <c r="E46" s="3">
         <v>249400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>275600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>298700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>308900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>265900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>268000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>249500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>260600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>308700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>272600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>271100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>277200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>245400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>263100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>246100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>290100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>270700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>211800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>193100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>234400</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="Y46" s="3" t="s">
         <v>12</v>
       </c>
@@ -3591,74 +3693,77 @@
       <c r="AC46" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E47" s="3">
         <v>1800</v>
-      </c>
-      <c r="E47" s="3">
-        <v>1900</v>
       </c>
       <c r="F47" s="3">
         <v>1900</v>
       </c>
       <c r="G47" s="3">
+        <v>1900</v>
+      </c>
+      <c r="H47" s="3">
         <v>2100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>3200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>3100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>6900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>6500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>5300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>13000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>78500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>28800</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>29300</v>
       </c>
       <c r="R47" s="3">
         <v>29300</v>
       </c>
       <c r="S47" s="3">
+        <v>29300</v>
+      </c>
+      <c r="T47" s="3">
         <v>19500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>21200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>19400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>19900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>3400</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="Y47" s="3" t="s">
         <v>12</v>
       </c>
@@ -3674,74 +3779,77 @@
       <c r="AC47" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>30700</v>
+      </c>
+      <c r="E48" s="3">
         <v>32400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>33500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>39200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>42300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>47000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>50000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>54000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>57100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>52600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>44100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>42900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>43500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>43600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>40200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>27200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>26600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>26100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>21800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>19800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>18900</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>12</v>
       </c>
@@ -3757,74 +3865,77 @@
       <c r="AC48" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>394400</v>
+      </c>
+      <c r="E49" s="3">
         <v>403200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>412200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>422300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>432000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>478100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>489800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>500800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>512700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>523500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>647300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1071000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>809700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>829300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>842800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>301700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>310000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>324600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>241500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>246500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>252700</v>
       </c>
-      <c r="X49" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="Y49" s="3" t="s">
         <v>12</v>
       </c>
@@ -3840,8 +3951,11 @@
       <c r="AC49" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3923,8 +4037,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4006,8 +4123,11 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4038,32 +4158,32 @@
       <c r="L52" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M52" s="3">
+      <c r="M52" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N52" s="3">
         <v>406000</v>
       </c>
-      <c r="N52" s="3">
-        <v>0</v>
-      </c>
       <c r="O52" s="3">
         <v>0</v>
       </c>
       <c r="P52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="3">
         <v>50000</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>50500</v>
       </c>
       <c r="R52" s="3">
         <v>50500</v>
       </c>
       <c r="S52" s="3">
-        <v>500</v>
+        <v>50500</v>
       </c>
       <c r="T52" s="3">
         <v>500</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>12</v>
+      <c r="U52" s="3">
+        <v>500</v>
       </c>
       <c r="V52" s="3" t="s">
         <v>12</v>
@@ -4080,8 +4200,8 @@
       <c r="Z52" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="AA52" s="3">
-        <v>0</v>
+      <c r="AA52" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="AB52" s="3">
         <v>0</v>
@@ -4089,8 +4209,11 @@
       <c r="AC52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4172,74 +4295,77 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>706800</v>
+      </c>
+      <c r="E54" s="3">
         <v>691400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>728000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>769500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>792200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>794200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>810900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>811100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>837000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>887400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1372600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1398000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1208800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1197100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1225900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>654800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>646600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>643100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>494500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>479300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>509400</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>12</v>
       </c>
@@ -4255,8 +4381,11 @@
       <c r="AC54" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4286,8 +4415,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4317,74 +4447,75 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>24200</v>
+      </c>
+      <c r="E57" s="3">
         <v>19200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>23700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>16800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>24400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>19100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>23000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>17600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>41400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>32800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>36700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>19100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>25700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>22500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>16900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>10900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>9900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>10300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>4400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>8800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>13600</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>12</v>
       </c>
@@ -4400,55 +4531,58 @@
       <c r="AC57" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>47800</v>
+      </c>
+      <c r="E58" s="3">
         <v>41700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>31300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>42500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>42400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>40600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>32700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>24300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>15300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>45600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>33100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>31300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>22500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>20300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>18000</v>
-      </c>
-      <c r="R58" s="3">
-        <v>15000</v>
       </c>
       <c r="S58" s="3">
         <v>15000</v>
@@ -4460,14 +4594,14 @@
         <v>15000</v>
       </c>
       <c r="V58" s="3">
+        <v>15000</v>
+      </c>
+      <c r="W58" s="3">
         <v>16300</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>15000</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="Y58" s="3" t="s">
         <v>12</v>
       </c>
@@ -4483,74 +4617,77 @@
       <c r="AC58" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>71600</v>
+      </c>
+      <c r="E59" s="3">
         <v>77900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>89800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>97900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>115600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>68900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>64300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>74300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>74200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>72900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>351900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>238000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>150600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>128700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>145900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>134800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>133300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>123700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>103200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>86700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>68700</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>12</v>
       </c>
@@ -4566,74 +4703,77 @@
       <c r="AC59" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>185700</v>
+      </c>
+      <c r="E60" s="3">
         <v>174800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>210400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>211500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>231500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>173300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>175500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>160800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>179100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>196100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>304000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>288400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>198900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>171500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>180900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>160700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>158200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>149000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>122600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>111700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>97200</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="Y60" s="3" t="s">
         <v>12</v>
       </c>
@@ -4649,74 +4789,77 @@
       <c r="AC60" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>312900</v>
+      </c>
+      <c r="E61" s="3">
         <v>324400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>324800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>362600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>363200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>375300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>388000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>397100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>387100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>424300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>385000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>393100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>351400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>348000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>339600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>162400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>166100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>169700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>173400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>177000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>229700</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -4732,74 +4875,77 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E62" s="3">
         <v>6100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>6600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>8600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>8500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>26900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>25100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>26700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>37500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>26300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>350700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>337400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>138300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>155700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>171600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>101200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>103000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>104000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>54300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>45200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>40700</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="Y62" s="3" t="s">
         <v>12</v>
       </c>
@@ -4815,8 +4961,11 @@
       <c r="AC62" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4898,8 +5047,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4981,8 +5133,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5064,74 +5219,77 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>505500</v>
+      </c>
+      <c r="E66" s="3">
         <v>505900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>542400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>582700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>603100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>576800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>589800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>584600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>603600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>647000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1047400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1054600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>760800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>747400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>766900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>502300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>505100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>500700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>352200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>336100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>370200</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>12</v>
       </c>
@@ -5147,8 +5305,11 @@
       <c r="AC66" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5178,8 +5339,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5261,8 +5423,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5344,8 +5509,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5401,7 +5569,7 @@
         <v>0</v>
       </c>
       <c r="U70" s="3">
-        <v>168000</v>
+        <v>0</v>
       </c>
       <c r="V70" s="3">
         <v>168000</v>
@@ -5410,7 +5578,7 @@
         <v>168000</v>
       </c>
       <c r="X70" s="3">
-        <v>0</v>
+        <v>168000</v>
       </c>
       <c r="Y70" s="3">
         <v>0</v>
@@ -5427,8 +5595,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5510,74 +5681,77 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-352800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-360300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-355100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-354900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-350100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-326100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-321500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-315400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-308100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-304500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-165300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-133400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-25100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-17900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-6600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-6200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-5200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-1000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-140700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-138400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-141500</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>12</v>
       </c>
@@ -5593,8 +5767,11 @@
       <c r="AC72" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5676,8 +5853,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5759,8 +5939,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5842,74 +6025,77 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>161200</v>
+      </c>
+      <c r="E76" s="3">
         <v>148100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>147900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>148700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>150900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>171300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>173600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>177500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>183200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>188500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>325200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>343400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>448000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>449800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>458900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>152500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>141600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>142400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-25800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-24800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-28800</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>12</v>
       </c>
@@ -5925,8 +6111,11 @@
       <c r="AC76" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6008,179 +6197,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45836</v>
+      </c>
+      <c r="E80" s="2">
         <v>45745</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45563</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45472</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45381</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45108</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45017</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44835</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44744</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44653</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44471</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44380</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44289</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44100</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44009</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43918</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43645</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>42735</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42462</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42369</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-4800</v>
       </c>
-      <c r="G81" s="3">
-        <v>-24000</v>
-      </c>
       <c r="H81" s="3">
+        <v>-25700</v>
+      </c>
+      <c r="I81" s="3">
         <v>-4900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-6100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-7300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-3700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-139200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-31900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-108200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-7300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-11300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-4100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>24900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>3000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>10900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>2500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-7400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-23400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-7100</v>
       </c>
-      <c r="AC81" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD81" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6210,91 +6408,95 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E83" s="3">
         <v>11800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>-18100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>13800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>14600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>16500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>-8500</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="K83" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L83" s="3">
         <v>12400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>12500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>23200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>18800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>12400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>12500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>11700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>8500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>7500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>7200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>6900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>7300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>14500</v>
-      </c>
-      <c r="X83" s="3">
-        <v>7300</v>
       </c>
       <c r="Y83" s="3">
         <v>7300</v>
       </c>
       <c r="Z83" s="3">
+        <v>7300</v>
+      </c>
+      <c r="AA83" s="3">
         <v>15700</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="AB83" s="3">
+      <c r="AB83" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC83" s="3">
         <v>9100</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6376,8 +6578,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6459,8 +6664,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6542,8 +6750,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6625,8 +6836,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6708,91 +6922,97 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>25900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-19300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>19300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>10300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>15200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-6000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>10400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-8300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>10800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>5200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-21000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>13100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>10600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>17300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-18000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>25400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>20800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>25500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>17700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>21000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>8000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>37100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>2200</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6822,91 +7042,95 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-600</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-100</v>
       </c>
       <c r="G91" s="3">
         <v>-100</v>
       </c>
       <c r="H91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I91" s="3">
         <v>-300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="AB91" s="3">
+      <c r="AB91" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-600</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6988,8 +7212,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7071,91 +7298,97 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>24100</v>
-      </c>
-      <c r="F94" s="3">
-        <v>-100</v>
       </c>
       <c r="G94" s="3">
         <v>-100</v>
       </c>
       <c r="H94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I94" s="3">
         <v>-1000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>33500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-15100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-56300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-52000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-221300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-13200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-46600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-17800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-7300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-7900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-6600</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7185,8 +7418,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7217,8 +7451,8 @@
       <c r="L96" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -7268,8 +7502,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7351,8 +7588,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7434,8 +7674,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7517,253 +7760,265 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-14700</v>
+      </c>
+      <c r="E100" s="3">
         <v>900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-42900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-7800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-4200</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>8200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-62200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>27400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-5400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>50700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>7700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>9200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>176300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-4300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-6100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>107500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-9900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-57100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>37400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>48800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-11100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-9000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>5500</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E101" s="3">
         <v>-500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1100</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="K101" s="3">
+      <c r="K101" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L101" s="3">
         <v>-200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1100</v>
-      </c>
-      <c r="N101" s="3">
-        <v>-200</v>
       </c>
       <c r="O101" s="3">
         <v>-200</v>
       </c>
       <c r="P101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-200</v>
-      </c>
-      <c r="X101" s="3">
-        <v>-300</v>
       </c>
       <c r="Y101" s="3">
         <v>-300</v>
       </c>
       <c r="Z101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AA101" s="3">
         <v>300</v>
       </c>
-      <c r="AA101" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="AB101" s="3">
+      <c r="AB101" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC101" s="3">
         <v>200</v>
       </c>
-      <c r="AC101" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-18800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>11100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>6800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-11800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>10100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-17700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>15300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-6600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-41700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-16600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-31700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-7200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>8600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>42600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>14400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-53800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>61700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>65800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>20900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-10200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>8000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1200</v>
       </c>
-      <c r="AC102" s="3" t="s">
+      <c r="AD102" s="3" t="s">
         <v>12</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BVS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BVS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="92">
   <si>
     <t>BVS</t>
   </si>
@@ -656,405 +656,417 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45927</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45836</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45745</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45563</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45472</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45381</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45108</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45017</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44835</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44744</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44653</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44471</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44380</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44289</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44100</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44009</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43918</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43645</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42735</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42462</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42369</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>157900</v>
+      </c>
+      <c r="E8" s="3">
         <v>138700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>147700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>123900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>153600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>139000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>151200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>129500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>135400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>120800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>137100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>119100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>125800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>128700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>140300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>117300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>130400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>108900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>109800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>81800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>98600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>85900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>136700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>78600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>97600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>160300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>274500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>65400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>71200</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>49100</v>
+      </c>
+      <c r="E9" s="3">
         <v>44400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>45600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>40800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>51000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>45400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>47600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>41100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>49100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>41900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>47900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>45100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>51600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>44100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>43700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>41600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>42600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>29800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>33500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>22200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>25100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>23400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>39100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>21400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>24100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>45100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>80400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>19200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>20200</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>108800</v>
+      </c>
+      <c r="E10" s="3">
         <v>94200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>102100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>83100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>102700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>93600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>103600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>88400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>86300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>78900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>89100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>73900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>74200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>84600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>96600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>75700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>87800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>79100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>76300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>59600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>73500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>62500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>97600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>57200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>73500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>115200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>194100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>46200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>51000</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1086,97 +1098,101 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E12" s="3">
         <v>2900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>3200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>3000</v>
       </c>
-      <c r="G12" s="3">
-        <v>3200</v>
-      </c>
       <c r="H12" s="3">
+        <v>3300</v>
+      </c>
+      <c r="I12" s="3">
         <v>3800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>4200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>2600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>3400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>3800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>5900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>4600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>6400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>6900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>7100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>6200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>4800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>2900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>3600</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>4700</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>2100</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>3100</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>5100</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>7900</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>3700</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1264,150 +1280,156 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E14" s="3">
         <v>300</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>3100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>2600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>44700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>77700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>4600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>314500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>700</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>3900</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>5700</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="X14" s="3">
         <v>900</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>3500</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="AA14" s="3">
+      <c r="AA14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB14" s="3">
         <v>3300</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>500</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>8800</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>200</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="E15" s="3">
         <v>1400</v>
       </c>
       <c r="F15" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G15" s="3">
         <v>1600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1800</v>
-      </c>
-      <c r="H15" s="3">
-        <v>2100</v>
       </c>
       <c r="I15" s="3">
         <v>2100</v>
       </c>
       <c r="J15" s="3">
+        <v>2100</v>
+      </c>
+      <c r="K15" s="3">
         <v>1800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2100</v>
-      </c>
-      <c r="L15" s="3">
-        <v>2300</v>
       </c>
       <c r="M15" s="3">
         <v>2300</v>
       </c>
       <c r="N15" s="3">
+        <v>2300</v>
+      </c>
+      <c r="O15" s="3">
         <v>2100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>2300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>2700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>3300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>2700</v>
-      </c>
-      <c r="T15" s="3">
-        <v>1900</v>
       </c>
       <c r="U15" s="3">
         <v>1900</v>
@@ -1416,34 +1438,37 @@
         <v>1900</v>
       </c>
       <c r="W15" s="3">
+        <v>1900</v>
+      </c>
+      <c r="X15" s="3">
         <v>2100</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>1700</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>3600</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>1800</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>2100</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>3800</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>11000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>2800</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1472,186 +1497,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>136200</v>
+      </c>
+      <c r="E17" s="3">
         <v>127400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>129300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>118900</v>
       </c>
-      <c r="G17" s="3">
-        <v>142500</v>
-      </c>
       <c r="H17" s="3">
+        <v>142800</v>
+      </c>
+      <c r="I17" s="3">
         <v>132800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>138000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>124200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>132800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>117100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>128500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>131900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>141500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>255500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>143600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>138700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>133600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>112100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>115600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>59800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>92700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>75900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>127200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>65700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>86800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>153500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>263600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>67400</v>
       </c>
-      <c r="AE17" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF17" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>21700</v>
+      </c>
+      <c r="E18" s="3">
         <v>11300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>18400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>5000</v>
       </c>
-      <c r="G18" s="3">
-        <v>11100</v>
-      </c>
       <c r="H18" s="3">
+        <v>10800</v>
+      </c>
+      <c r="I18" s="3">
         <v>6200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>13200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>5200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>8600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-12800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-15700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-126800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-3300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-21400</v>
-      </c>
-      <c r="S18" s="3">
-        <v>-3200</v>
       </c>
       <c r="T18" s="3">
         <v>-3200</v>
       </c>
       <c r="U18" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="V18" s="3">
         <v>-5800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>22000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>5900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>10000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>9500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>12900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>10800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>6900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>10900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF18" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1683,236 +1715,243 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-700</v>
-      </c>
-      <c r="L20" s="3">
-        <v>500</v>
       </c>
       <c r="M20" s="3">
         <v>500</v>
       </c>
       <c r="N20" s="3">
+        <v>500</v>
+      </c>
+      <c r="O20" s="3">
         <v>-100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-9400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-3200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1400</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>-3300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>2400</v>
-      </c>
-      <c r="W20" s="3">
-        <v>300</v>
       </c>
       <c r="X20" s="3">
         <v>300</v>
       </c>
       <c r="Y20" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-600</v>
       </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
       <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="3">
         <v>-700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>500</v>
       </c>
-      <c r="AE20" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E21" s="3">
         <v>12600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>19300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>5800</v>
       </c>
-      <c r="G21" s="3">
-        <v>14100</v>
-      </c>
       <c r="H21" s="3">
+        <v>13800</v>
+      </c>
+      <c r="I21" s="3">
         <v>8900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>15100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>6900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>5400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>5500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>10400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-10600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-108200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>5900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-7100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>7100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>5400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-1600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>31600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>13000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>17500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>22200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>17800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>17500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>22600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>44000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>7600</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E22" s="3">
         <v>6200</v>
-      </c>
-      <c r="E22" s="3">
-        <v>7500</v>
       </c>
       <c r="F22" s="3">
         <v>7500</v>
       </c>
       <c r="G22" s="3">
+        <v>7500</v>
+      </c>
+      <c r="H22" s="3">
         <v>9000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>9500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>9900</v>
-      </c>
-      <c r="J22" s="3">
-        <v>10300</v>
       </c>
       <c r="K22" s="3">
         <v>10300</v>
       </c>
       <c r="L22" s="3">
+        <v>10300</v>
+      </c>
+      <c r="M22" s="3">
         <v>10100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>10600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>9700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>7400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>3600</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
       <c r="R22" s="3">
         <v>0</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>12</v>
+      <c r="S22" s="3">
+        <v>0</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>12</v>
@@ -1923,213 +1962,222 @@
       <c r="V22" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="W22" s="3">
+      <c r="W22" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="X22" s="3">
         <v>3000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>1900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>3200</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="AA22" s="3">
+      <c r="AA22" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB22" s="3">
         <v>3900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>9400</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>15900</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>3900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E23" s="3">
         <v>4700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>10300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-3400</v>
       </c>
-      <c r="G23" s="3">
-        <v>200</v>
-      </c>
       <c r="H23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I23" s="3">
         <v>-5300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-41600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-5500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-8400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-8200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-4400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-100200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-32400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-130600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-6500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-19500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-4600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-3200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-9100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>24500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>3100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>8300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>4400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>10500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>6200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-5700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-5400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-5300</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E24" s="3">
         <v>700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-100</v>
-      </c>
-      <c r="G24" s="3">
-        <v>600</v>
       </c>
       <c r="H24" s="3">
         <v>600</v>
       </c>
       <c r="I24" s="3">
+        <v>600</v>
+      </c>
+      <c r="J24" s="3">
         <v>-7300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-11000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-29500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-5100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-2700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-100</v>
       </c>
-      <c r="Z24" s="3">
-        <v>0</v>
-      </c>
       <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="3">
         <v>900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2217,186 +2265,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E26" s="3">
         <v>4000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>9300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-3300</v>
       </c>
-      <c r="G26" s="3">
-        <v>-300</v>
-      </c>
       <c r="H26" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I26" s="3">
         <v>-5800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-34200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-6400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-7700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-8800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-4700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-100000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-21500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-101000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-7700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-14400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-2300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-10800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>24500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>8000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>4500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>10500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>5300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-6700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-6000</v>
       </c>
-      <c r="AE26" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF26" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E27" s="3">
         <v>3200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>7500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2600</v>
       </c>
-      <c r="G27" s="3">
-        <v>-200</v>
-      </c>
       <c r="H27" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I27" s="3">
         <v>-5200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-25700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-4900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-6100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-7300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-3700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-139200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-13200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-72800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-7000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-10900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-4100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>24900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>3000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>10900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>2700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-5700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-12200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-7100</v>
       </c>
-      <c r="AE27" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF27" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2484,8 +2541,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2520,25 +2580,25 @@
         <v>0</v>
       </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>-59500</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-18700</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-35400</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-300</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-400</v>
       </c>
-      <c r="S29" s="3">
-        <v>0</v>
-      </c>
-      <c r="T29" s="3" t="s">
-        <v>12</v>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>12</v>
@@ -2546,8 +2606,8 @@
       <c r="V29" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
+      <c r="W29" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="X29" s="3">
         <v>0</v>
@@ -2555,26 +2615,29 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="AA29" s="3">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-200</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-1600</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-11200</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="AE29" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2662,8 +2725,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2751,186 +2817,195 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>700</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-500</v>
       </c>
       <c r="M32" s="3">
         <v>-500</v>
       </c>
       <c r="N32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="O32" s="3">
         <v>100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>9400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>3200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1400</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>3300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-2400</v>
-      </c>
-      <c r="W32" s="3">
-        <v>-300</v>
       </c>
       <c r="X32" s="3">
         <v>-300</v>
       </c>
       <c r="Y32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Z32" s="3">
         <v>1900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>2400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>600</v>
       </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
       <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="3">
         <v>700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-500</v>
       </c>
-      <c r="AE32" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E33" s="3">
         <v>3200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>7500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2600</v>
       </c>
-      <c r="G33" s="3">
-        <v>-200</v>
-      </c>
       <c r="H33" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I33" s="3">
         <v>-5200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-25700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-4900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-6100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-7300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-3700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-139200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-31900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-108200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-7300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-11300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-4100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>24900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>3000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>10900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>2500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-7400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-23400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-7100</v>
       </c>
-      <c r="AE33" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF33" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3018,191 +3093,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E35" s="3">
         <v>3200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>7500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2600</v>
       </c>
-      <c r="G35" s="3">
-        <v>-200</v>
-      </c>
       <c r="H35" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I35" s="3">
         <v>-5200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-25700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-4900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-6100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-7300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-3700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-139200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-31900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-108200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-7300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-11300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-4100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>24900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>3000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>10900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>2500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-7400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-23400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-7100</v>
       </c>
-      <c r="AE35" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF35" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45927</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45836</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45745</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45563</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45472</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45381</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45108</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45017</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44835</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44744</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44653</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44471</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44380</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44289</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44100</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44009</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43918</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43645</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42735</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42462</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42369</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3234,8 +3318,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3267,80 +3352,81 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>51200</v>
+      </c>
+      <c r="E41" s="3">
         <v>42200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>32900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>22800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>41600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>43100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>32000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>25200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>37000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>26800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>29400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>47100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>30200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>34400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>41000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>27400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>43900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>80900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>136100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>124200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>86800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>72500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>126200</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="AA41" s="3" t="s">
         <v>12</v>
       </c>
@@ -3356,8 +3442,11 @@
       <c r="AE41" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3445,80 +3534,83 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>128300</v>
+      </c>
+      <c r="E43" s="3">
         <v>130400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>132400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>118100</v>
       </c>
-      <c r="G43" s="3">
-        <v>127500</v>
-      </c>
       <c r="H43" s="3">
+        <v>127400</v>
+      </c>
+      <c r="I43" s="3">
         <v>121900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>137300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>125500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>123000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>112900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>119600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>118500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>136600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>132200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>143000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>119300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>125000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>105400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>102000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>89500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>88400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>80900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>67400</v>
       </c>
-      <c r="Z43" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="AA43" s="3" t="s">
         <v>12</v>
       </c>
@@ -3534,80 +3626,83 @@
       <c r="AE43" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>82200</v>
+      </c>
+      <c r="E44" s="3">
         <v>96300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>96500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>94000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>92500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>90000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>87600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>97000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>91300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>97600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>96300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>88000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>82900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>77000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>69100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>64700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>61700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>36600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>34000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>39800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>29100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>34700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>33800</v>
       </c>
-      <c r="Z44" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="AA44" s="3" t="s">
         <v>12</v>
       </c>
@@ -3623,8 +3718,11 @@
       <c r="AE44" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3640,15 +3738,15 @@
       <c r="G45" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I45" s="3">
         <v>26700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>28400</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>12</v>
       </c>
@@ -3658,45 +3756,45 @@
       <c r="M45" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N45" s="3">
+      <c r="N45" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O45" s="3">
         <v>37900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>21100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>27600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>24100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>34000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>32400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>23200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>17900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>17200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>7500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>5000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>7100</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="AA45" s="3" t="s">
         <v>12</v>
       </c>
@@ -3712,80 +3810,83 @@
       <c r="AE45" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>272800</v>
+      </c>
+      <c r="E46" s="3">
         <v>280900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>275200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>249400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>275600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>298700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>308900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>265900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>268000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>249500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>260600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>308700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>272600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>271100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>277200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>245400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>263100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>246100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>290100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>270700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>211800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>193100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>234400</v>
       </c>
-      <c r="Z46" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="AA46" s="3" t="s">
         <v>12</v>
       </c>
@@ -3801,8 +3902,11 @@
       <c r="AE46" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3810,71 +3914,71 @@
         <v>2300</v>
       </c>
       <c r="E47" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F47" s="3">
         <v>1700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1800</v>
-      </c>
-      <c r="G47" s="3">
-        <v>1900</v>
       </c>
       <c r="H47" s="3">
         <v>1900</v>
       </c>
       <c r="I47" s="3">
+        <v>1900</v>
+      </c>
+      <c r="J47" s="3">
         <v>2100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>3200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>3100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>6900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>6500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>5300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>13000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>78500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>28800</v>
-      </c>
-      <c r="S47" s="3">
-        <v>29300</v>
       </c>
       <c r="T47" s="3">
         <v>29300</v>
       </c>
       <c r="U47" s="3">
+        <v>29300</v>
+      </c>
+      <c r="V47" s="3">
         <v>19500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>21200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>19400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>19900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>3400</v>
       </c>
-      <c r="Z47" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="AA47" s="3" t="s">
         <v>12</v>
       </c>
@@ -3890,80 +3994,83 @@
       <c r="AE47" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E48" s="3">
         <v>28800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>30700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>32400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>33500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>39200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>42300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>47000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>50000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>54000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>57100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>52600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>44100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>42900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>43500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>43600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>40200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>27200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>26600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>26100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>21800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>19800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>18900</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="AA48" s="3" t="s">
         <v>12</v>
       </c>
@@ -3979,80 +4086,83 @@
       <c r="AE48" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>375900</v>
+      </c>
+      <c r="E49" s="3">
         <v>384900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>394400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>403200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>412200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>422300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>432000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>478100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>489800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>500800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>512700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>523500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>647300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1071000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>809700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>829300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>842800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>301700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>310000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>324600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>241500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>246500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>252700</v>
       </c>
-      <c r="Z49" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="AA49" s="3" t="s">
         <v>12</v>
       </c>
@@ -4068,8 +4178,11 @@
       <c r="AE49" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4157,8 +4270,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4246,8 +4362,11 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4284,32 +4403,32 @@
       <c r="N52" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="O52" s="3">
+      <c r="O52" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="P52" s="3">
         <v>406000</v>
       </c>
-      <c r="P52" s="3">
-        <v>0</v>
-      </c>
       <c r="Q52" s="3">
         <v>0</v>
       </c>
       <c r="R52" s="3">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3">
         <v>50000</v>
-      </c>
-      <c r="S52" s="3">
-        <v>50500</v>
       </c>
       <c r="T52" s="3">
         <v>50500</v>
       </c>
       <c r="U52" s="3">
-        <v>500</v>
+        <v>50500</v>
       </c>
       <c r="V52" s="3">
         <v>500</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>12</v>
+      <c r="W52" s="3">
+        <v>500</v>
       </c>
       <c r="X52" s="3" t="s">
         <v>12</v>
@@ -4326,8 +4445,8 @@
       <c r="AB52" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="AC52" s="3">
-        <v>0</v>
+      <c r="AC52" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="AD52" s="3">
         <v>0</v>
@@ -4335,8 +4454,11 @@
       <c r="AE52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4424,80 +4546,83 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>683600</v>
+      </c>
+      <c r="E54" s="3">
         <v>701600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>706800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>691400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>728000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>769500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>792200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>794200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>810900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>811100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>837000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>887400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1372600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1398000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1208800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1197100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1225900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>654800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>646600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>643100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>494500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>479300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>509400</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="AA54" s="3" t="s">
         <v>12</v>
       </c>
@@ -4513,8 +4638,11 @@
       <c r="AE54" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4546,8 +4674,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4579,80 +4708,81 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E57" s="3">
         <v>26600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>24200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>19200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>23700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>16800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>24400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>19100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>23000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>17600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>41400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>32800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>36700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>19100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>25700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>22500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>16900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>10900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>9900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>10300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>4400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>8800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>13600</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="AA57" s="3" t="s">
         <v>12</v>
       </c>
@@ -4668,61 +4798,64 @@
       <c r="AE57" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>19200</v>
+      </c>
+      <c r="E58" s="3">
         <v>15700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>47800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>41700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>31300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>42500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>42400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>40600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>32700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>24300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>15300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>45600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>33100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>31300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>22500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>20300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>18000</v>
-      </c>
-      <c r="T58" s="3">
-        <v>15000</v>
       </c>
       <c r="U58" s="3">
         <v>15000</v>
@@ -4734,14 +4867,14 @@
         <v>15000</v>
       </c>
       <c r="X58" s="3">
+        <v>15000</v>
+      </c>
+      <c r="Y58" s="3">
         <v>16300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>15000</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="AA58" s="3" t="s">
         <v>12</v>
       </c>
@@ -4757,80 +4890,83 @@
       <c r="AE58" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>78600</v>
+      </c>
+      <c r="E59" s="3">
         <v>76000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>71600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>77900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>89800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>97900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>115600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>68900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>64300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>74300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>74200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>72900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>351900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>238000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>150600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>128700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>145900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>134800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>133300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>123700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>103200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>86700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>68700</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="AA59" s="3" t="s">
         <v>12</v>
       </c>
@@ -4846,80 +4982,83 @@
       <c r="AE59" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>160400</v>
+      </c>
+      <c r="E60" s="3">
         <v>161800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>185700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>174800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>210400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>211500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>231500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>173300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>175500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>160800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>179100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>196100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>304000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>288400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>198900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>171500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>180900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>160700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>158200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>149000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>122600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>111700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>97200</v>
       </c>
-      <c r="Z60" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="AA60" s="3" t="s">
         <v>12</v>
       </c>
@@ -4935,80 +5074,83 @@
       <c r="AE60" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>292100</v>
+      </c>
+      <c r="E61" s="3">
         <v>325500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>312900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>324400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>324800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>362600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>363200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>375300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>388000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>397100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>387100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>424300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>385000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>393100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>351400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>348000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>339600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>162400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>166100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>169700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>173400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>177000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>229700</v>
       </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
       <c r="AA61" s="3">
         <v>0</v>
       </c>
@@ -5024,80 +5166,83 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>6300</v>
+        <v>2200</v>
       </c>
       <c r="E62" s="3">
         <v>6300</v>
       </c>
       <c r="F62" s="3">
+        <v>6300</v>
+      </c>
+      <c r="G62" s="3">
         <v>6100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>6600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>8600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>8500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>26900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>25100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>26700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>37500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>26300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>350700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>337400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>138300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>155700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>171600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>101200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>103000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>104000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>54300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>45200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>40700</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="AA62" s="3" t="s">
         <v>12</v>
       </c>
@@ -5113,8 +5258,11 @@
       <c r="AE62" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5202,8 +5350,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5291,8 +5442,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5380,80 +5534,83 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>455100</v>
+      </c>
+      <c r="E66" s="3">
         <v>494300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>505500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>505900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>542400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>582700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>603100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>576800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>589800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>584600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>603600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>647000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1047400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1054600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>760800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>747400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>766900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>502300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>505100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>500700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>352200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>336100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>370200</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="AA66" s="3" t="s">
         <v>12</v>
       </c>
@@ -5469,8 +5626,11 @@
       <c r="AE66" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5502,8 +5662,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5591,8 +5752,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5680,8 +5844,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5743,7 +5910,7 @@
         <v>0</v>
       </c>
       <c r="W70" s="3">
-        <v>168000</v>
+        <v>0</v>
       </c>
       <c r="X70" s="3">
         <v>168000</v>
@@ -5752,7 +5919,7 @@
         <v>168000</v>
       </c>
       <c r="Z70" s="3">
-        <v>0</v>
+        <v>168000</v>
       </c>
       <c r="AA70" s="3">
         <v>0</v>
@@ -5769,8 +5936,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5858,80 +6028,83 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-334900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-349700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-352800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-360300</v>
       </c>
-      <c r="G72" s="3">
-        <v>-355100</v>
-      </c>
       <c r="H72" s="3">
+        <v>-357700</v>
+      </c>
+      <c r="I72" s="3">
         <v>-354900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-350100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-326100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-321500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-315400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-308100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-304500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-165300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-133400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-25100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-17900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-6600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-6200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-5200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-1000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-140700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-138400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-141500</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="AA72" s="3" t="s">
         <v>12</v>
       </c>
@@ -5947,8 +6120,11 @@
       <c r="AE72" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6036,8 +6212,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6125,8 +6304,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6214,80 +6396,83 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>184100</v>
+      </c>
+      <c r="E76" s="3">
         <v>166100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>161200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>148100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>147900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>148700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>150900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>171300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>173600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>177500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>183200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>188500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>325200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>343400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>448000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>449800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>458900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>152500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>141600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>142400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-25800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-24800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-28800</v>
       </c>
-      <c r="Z76" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="AA76" s="3" t="s">
         <v>12</v>
       </c>
@@ -6303,8 +6488,11 @@
       <c r="AE76" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6392,191 +6580,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45927</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45836</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45745</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45563</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45472</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45381</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45108</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45017</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44835</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44744</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44653</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44471</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44380</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44289</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44100</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44009</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43918</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43645</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42735</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42462</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42369</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E81" s="3">
         <v>3200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>7500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2600</v>
       </c>
-      <c r="G81" s="3">
-        <v>-200</v>
-      </c>
       <c r="H81" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I81" s="3">
         <v>-5200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-25700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-4900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-6100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-7300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-3700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-139200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-31900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-108200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-7300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-11300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-4100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>24900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>3000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>10900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>2500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-7400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-23400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-7100</v>
       </c>
-      <c r="AE81" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF81" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6608,97 +6805,101 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>-18000</v>
+      </c>
+      <c r="E83" s="3">
         <v>12300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>13100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>11800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>-18100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>13800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>14600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>16500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>-8500</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N83" s="3">
         <v>12400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>12500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>23200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>18800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>12400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>12500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>11700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>8500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>7500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>7200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>6900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>7300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>14500</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>7300</v>
       </c>
       <c r="AA83" s="3">
         <v>7300</v>
       </c>
       <c r="AB83" s="3">
+        <v>7300</v>
+      </c>
+      <c r="AC83" s="3">
         <v>15700</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="AD83" s="3">
+      <c r="AD83" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE83" s="3">
         <v>9100</v>
       </c>
-      <c r="AE83" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6786,8 +6987,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6875,8 +7079,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6964,8 +7171,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7053,8 +7263,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7142,97 +7355,103 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>38000</v>
+      </c>
+      <c r="E89" s="3">
         <v>30100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>25900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-19300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>19300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>10300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>15200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-6000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>10400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-8300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>10800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>5200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-21000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>13100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>10600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>17300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-18000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>25400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>20800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>25500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>17700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>21000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>8000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>37100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2200</v>
       </c>
-      <c r="AE89" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7264,97 +7483,101 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-600</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-100</v>
       </c>
       <c r="I91" s="3">
         <v>-100</v>
       </c>
       <c r="J91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K91" s="3">
         <v>-300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1300</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="AD91" s="3">
+      <c r="AD91" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-600</v>
       </c>
-      <c r="AE91" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7442,8 +7665,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7531,97 +7757,103 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>24100</v>
-      </c>
-      <c r="H94" s="3">
-        <v>-100</v>
       </c>
       <c r="I94" s="3">
         <v>-100</v>
       </c>
       <c r="J94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K94" s="3">
         <v>-1000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>33500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-15100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-56300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-52000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-4700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-221300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-13200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-46600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-17800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-7300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-7900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-6600</v>
       </c>
-      <c r="AE94" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7653,8 +7885,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7691,8 +7924,8 @@
       <c r="N96" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -7742,8 +7975,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7831,8 +8067,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7920,8 +8159,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8009,271 +8251,283 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-28400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-20000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-14700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-42900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-7800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-4200</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>8200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-62200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>27400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-5400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>50700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>7700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>9200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>176300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-4300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-6100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>107500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-9900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-57100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>37400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>48800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-11100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-9000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>5500</v>
       </c>
-      <c r="AE100" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E101" s="3">
         <v>500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1100</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M101" s="3">
+      <c r="M101" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N101" s="3">
         <v>-200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1100</v>
-      </c>
-      <c r="P101" s="3">
-        <v>-200</v>
       </c>
       <c r="Q101" s="3">
         <v>-200</v>
       </c>
       <c r="R101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S101" s="3">
         <v>-100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-200</v>
-      </c>
-      <c r="Z101" s="3">
-        <v>-300</v>
       </c>
       <c r="AA101" s="3">
         <v>-300</v>
       </c>
       <c r="AB101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AC101" s="3">
         <v>300</v>
       </c>
-      <c r="AC101" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="AD101" s="3">
+      <c r="AD101" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE101" s="3">
         <v>200</v>
       </c>
-      <c r="AE101" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E102" s="3">
         <v>9300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>10100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-18800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>11100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>6800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-11800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>10100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-17700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>15300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-6600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-41700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-16600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-31700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-7200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>8600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>42600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>14400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-53800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>61700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>65800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>20900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-10200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>8000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1200</v>
       </c>
-      <c r="AE102" s="3" t="s">
+      <c r="AF102" s="3" t="s">
         <v>12</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BVS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BVS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="92">
   <si>
     <t>BVS</t>
   </si>
@@ -656,417 +656,430 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="20" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46109</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45927</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45836</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45745</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45563</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45472</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45381</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45108</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45017</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44835</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44744</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44653</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44471</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44380</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44289</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44100</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44009</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43918</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43645</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42735</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42462</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42369</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>132100</v>
+      </c>
+      <c r="E8" s="3">
         <v>157900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>138700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>147700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>123900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>153600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>139000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>151200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>129500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>135400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>120800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>137100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>119100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>125800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>128700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>140300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>117300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>130400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>108900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>109800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>81800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>98600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>85900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>136700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>78600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>97600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>160300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>274500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>65400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>71200</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>41300</v>
+      </c>
+      <c r="E9" s="3">
         <v>49100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>44400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>45600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>40800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>51000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>45400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>47600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>41100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>49100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>41900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>47900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>45100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>51600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>44100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>43700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>41600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>42600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>29800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>33500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>22200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>25100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>23400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>39100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>21400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>24100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>45100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>80400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>19200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>20200</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>90800</v>
+      </c>
+      <c r="E10" s="3">
         <v>108800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>94200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>102100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>83100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>102700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>93600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>103600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>88400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>86300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>78900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>89100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>73900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>74200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>84600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>96600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>75700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>87800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>79100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>76300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>59600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>73500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>62500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>97600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>57200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>73500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>115200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>194100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>46200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>51000</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1099,100 +1112,104 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E12" s="3">
         <v>3000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>2900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>3200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>3000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>3300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>3800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>4200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>2600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>3000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>3400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>3800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>5900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>4600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>6400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>6900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>7100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>6200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>4800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>2900</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>3600</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>4700</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>2100</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>3100</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>5100</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>7900</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>3700</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1283,156 +1300,162 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>500</v>
+      </c>
+      <c r="E14" s="3">
         <v>2200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>300</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>3100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>44700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>77700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>4600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>314500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>700</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>3900</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>5700</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="X14" s="3">
+      <c r="X14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y14" s="3">
         <v>900</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>3500</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="AB14" s="3">
+      <c r="AB14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC14" s="3">
         <v>3300</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>500</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>8800</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>200</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E15" s="3">
         <v>1300</v>
-      </c>
-      <c r="E15" s="3">
-        <v>1400</v>
       </c>
       <c r="F15" s="3">
         <v>1400</v>
       </c>
       <c r="G15" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H15" s="3">
         <v>1600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1800</v>
-      </c>
-      <c r="I15" s="3">
-        <v>2100</v>
       </c>
       <c r="J15" s="3">
         <v>2100</v>
       </c>
       <c r="K15" s="3">
+        <v>2100</v>
+      </c>
+      <c r="L15" s="3">
         <v>1800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2100</v>
-      </c>
-      <c r="M15" s="3">
-        <v>2300</v>
       </c>
       <c r="N15" s="3">
         <v>2300</v>
       </c>
       <c r="O15" s="3">
+        <v>2300</v>
+      </c>
+      <c r="P15" s="3">
         <v>2100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>2300</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>2700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>3300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>2700</v>
-      </c>
-      <c r="U15" s="3">
-        <v>1900</v>
       </c>
       <c r="V15" s="3">
         <v>1900</v>
@@ -1441,34 +1464,37 @@
         <v>1900</v>
       </c>
       <c r="X15" s="3">
+        <v>1900</v>
+      </c>
+      <c r="Y15" s="3">
         <v>2100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>1700</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>3600</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>1800</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>2100</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>3800</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>11000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>2800</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1498,192 +1524,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>123200</v>
+      </c>
+      <c r="E17" s="3">
         <v>136200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>127400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>129300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>118900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>142800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>132800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>138000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>124200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>132800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>117100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>128500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>131900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>141500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>255500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>143600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>138700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>133600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>112100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>115600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>59800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>92700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>75900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>127200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>65700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>86800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>153500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>263600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>67400</v>
       </c>
-      <c r="AF17" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG17" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E18" s="3">
         <v>21700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>11300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>18400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>5000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>10800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>6200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>13200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>5200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>8600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-12800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-15700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-126800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-3300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-21400</v>
-      </c>
-      <c r="T18" s="3">
-        <v>-3200</v>
       </c>
       <c r="U18" s="3">
         <v>-3200</v>
       </c>
       <c r="V18" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="W18" s="3">
         <v>-5800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>22000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>5900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>10000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>9500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>12900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>10800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>6900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>10900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-2000</v>
       </c>
-      <c r="AF18" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG18" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1716,245 +1749,252 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-700</v>
-      </c>
-      <c r="M20" s="3">
-        <v>500</v>
       </c>
       <c r="N20" s="3">
         <v>500</v>
       </c>
       <c r="O20" s="3">
+        <v>500</v>
+      </c>
+      <c r="P20" s="3">
         <v>-100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-9400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-3200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1400</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>-3300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>2400</v>
-      </c>
-      <c r="X20" s="3">
-        <v>300</v>
       </c>
       <c r="Y20" s="3">
         <v>300</v>
       </c>
       <c r="Z20" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-2400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-600</v>
       </c>
-      <c r="AC20" s="3">
-        <v>0</v>
-      </c>
       <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="3">
         <v>-700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>500</v>
       </c>
-      <c r="AF20" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E21" s="3">
         <v>23000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>12600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>19300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>5800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>13800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>8900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>15100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>6900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>5400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>5500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>10400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-10600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-108200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>5900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-7100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>7100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>5400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-1600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>31600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>13000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>17500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>22200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>17800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>17500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>22600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>44000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>7600</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E22" s="3">
         <v>5300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>6200</v>
-      </c>
-      <c r="F22" s="3">
-        <v>7500</v>
       </c>
       <c r="G22" s="3">
         <v>7500</v>
       </c>
       <c r="H22" s="3">
+        <v>7500</v>
+      </c>
+      <c r="I22" s="3">
         <v>9000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>9500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>9900</v>
-      </c>
-      <c r="K22" s="3">
-        <v>10300</v>
       </c>
       <c r="L22" s="3">
         <v>10300</v>
       </c>
       <c r="M22" s="3">
+        <v>10300</v>
+      </c>
+      <c r="N22" s="3">
         <v>10100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>10600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>9700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>7400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>3600</v>
       </c>
-      <c r="R22" s="3">
-        <v>0</v>
-      </c>
       <c r="S22" s="3">
         <v>0</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>12</v>
+      <c r="T22" s="3">
+        <v>0</v>
       </c>
       <c r="U22" s="3" t="s">
         <v>12</v>
@@ -1965,219 +2005,228 @@
       <c r="W22" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="X22" s="3">
+      <c r="X22" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y22" s="3">
         <v>3000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>1900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>3200</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="AB22" s="3">
+      <c r="AB22" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC22" s="3">
         <v>3900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>9400</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>15900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>3900</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E23" s="3">
         <v>14100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>4700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>10300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-3400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-5300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-41600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-8400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-8200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-4400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-100200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-32400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-130600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-6500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-19500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-4600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-3200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-9100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>24500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>3100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>8300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>4400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>10500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>6200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-2500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-5700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-5400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-5300</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>600</v>
+      </c>
+      <c r="E24" s="3">
         <v>-3200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-100</v>
-      </c>
-      <c r="H24" s="3">
-        <v>600</v>
       </c>
       <c r="I24" s="3">
         <v>600</v>
       </c>
       <c r="J24" s="3">
+        <v>600</v>
+      </c>
+      <c r="K24" s="3">
         <v>-7300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-29500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-5100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-2700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-100</v>
       </c>
-      <c r="AA24" s="3">
-        <v>0</v>
-      </c>
       <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3">
         <v>900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2268,192 +2317,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E26" s="3">
         <v>17300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>4000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>9300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-3300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-5800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-34200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-6400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-7700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-8800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-4700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-100000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-21500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-101000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-7700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-14400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-2300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-10800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>24500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>8000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>4500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>10500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>5300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-6700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-6000</v>
       </c>
-      <c r="AF26" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG26" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E27" s="3">
         <v>14800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>7500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-2600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-5200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-25700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-4900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-6100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-7300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-3700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-139200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-13200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-72800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-7000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-10900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-4100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>24900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>3000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>10900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>2700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-5700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-12200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-7100</v>
       </c>
-      <c r="AF27" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG27" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2544,8 +2602,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2583,25 +2644,25 @@
         <v>0</v>
       </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>-59500</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-18700</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-35400</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-300</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-400</v>
       </c>
-      <c r="T29" s="3">
-        <v>0</v>
-      </c>
-      <c r="U29" s="3" t="s">
-        <v>12</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>12</v>
@@ -2609,8 +2670,8 @@
       <c r="W29" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
+      <c r="X29" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="Y29" s="3">
         <v>0</v>
@@ -2618,26 +2679,29 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="AB29" s="3">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-200</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>-11200</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="AF29" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2728,8 +2792,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2820,192 +2887,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>700</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-500</v>
       </c>
       <c r="N32" s="3">
         <v>-500</v>
       </c>
       <c r="O32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="P32" s="3">
         <v>100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>9400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>3200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1400</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>3300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-2400</v>
-      </c>
-      <c r="X32" s="3">
-        <v>-300</v>
       </c>
       <c r="Y32" s="3">
         <v>-300</v>
       </c>
       <c r="Z32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AA32" s="3">
         <v>1900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>2400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>600</v>
       </c>
-      <c r="AC32" s="3">
-        <v>0</v>
-      </c>
       <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3">
         <v>700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-500</v>
       </c>
-      <c r="AF32" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E33" s="3">
         <v>14800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>7500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-2600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-5200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-25700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-4900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-6100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-7300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-3700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-139200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-31900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-108200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-7300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-11300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-4100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>24900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>3000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>10900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>2500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-7400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-23400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-7100</v>
       </c>
-      <c r="AF33" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG33" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3096,197 +3172,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E35" s="3">
         <v>14800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>7500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-2600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-5200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-25700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-4900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-6100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-7300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-3700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-139200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-31900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-108200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-7300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-11300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-4100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>24900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>3000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>10900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>2500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-7400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-23400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-7100</v>
       </c>
-      <c r="AF35" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG35" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46109</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45927</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45836</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45745</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45563</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45472</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45381</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45108</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45017</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44835</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44744</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44653</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44471</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44380</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44289</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44100</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44009</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43918</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43645</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42735</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42462</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42369</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3319,8 +3404,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3353,83 +3439,84 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>35800</v>
+      </c>
+      <c r="E41" s="3">
         <v>51200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>42200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>32900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>22800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>41600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>43100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>32000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>25200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>37000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>26800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>29400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>47100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>30200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>34400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>41000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>27400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>43900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>80900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>136100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>124200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>86800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>72500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>126200</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="AB41" s="3" t="s">
         <v>12</v>
       </c>
@@ -3445,8 +3532,11 @@
       <c r="AF41" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3537,83 +3627,86 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>120500</v>
+      </c>
+      <c r="E43" s="3">
         <v>128300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>130400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>132400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>118100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>127400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>121900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>137300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>125500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>123000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>112900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>119600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>118500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>136600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>132200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>143000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>119300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>125000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>105400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>102000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>89500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>88400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>80900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>67400</v>
       </c>
-      <c r="AA43" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="AB43" s="3" t="s">
         <v>12</v>
       </c>
@@ -3629,83 +3722,86 @@
       <c r="AF43" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>83200</v>
+      </c>
+      <c r="E44" s="3">
         <v>82200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>96300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>96500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>94000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>92500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>90000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>87600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>97000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>91300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>97600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>96300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>88000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>82900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>77000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>69100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>64700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>61700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>36600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>34000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>39800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>29100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>34700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>33800</v>
       </c>
-      <c r="AA44" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="AB44" s="3" t="s">
         <v>12</v>
       </c>
@@ -3721,8 +3817,11 @@
       <c r="AF44" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3741,15 +3840,15 @@
       <c r="H45" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J45" s="3">
         <v>26700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>28400</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>12</v>
       </c>
@@ -3759,45 +3858,45 @@
       <c r="N45" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="P45" s="3">
         <v>37900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>21100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>27600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>24100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>34000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>32400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>23200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>17900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>17200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>7500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>5000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>7100</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="AB45" s="3" t="s">
         <v>12</v>
       </c>
@@ -3813,83 +3912,86 @@
       <c r="AF45" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>249800</v>
+      </c>
+      <c r="E46" s="3">
         <v>272800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>280900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>275200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>249400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>275600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>298700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>308900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>265900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>268000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>249500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>260600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>308700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>272600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>271100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>277200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>245400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>263100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>246100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>290100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>270700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>211800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>193100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>234400</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="AB46" s="3" t="s">
         <v>12</v>
       </c>
@@ -3905,83 +4007,86 @@
       <c r="AF46" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>2300</v>
+        <v>2100</v>
       </c>
       <c r="E47" s="3">
         <v>2300</v>
       </c>
       <c r="F47" s="3">
+        <v>2300</v>
+      </c>
+      <c r="G47" s="3">
         <v>1700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1800</v>
-      </c>
-      <c r="H47" s="3">
-        <v>1900</v>
       </c>
       <c r="I47" s="3">
         <v>1900</v>
       </c>
       <c r="J47" s="3">
+        <v>1900</v>
+      </c>
+      <c r="K47" s="3">
         <v>2100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>3200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>3100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>6900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>6500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>5300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>13000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>78500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>28800</v>
-      </c>
-      <c r="T47" s="3">
-        <v>29300</v>
       </c>
       <c r="U47" s="3">
         <v>29300</v>
       </c>
       <c r="V47" s="3">
+        <v>29300</v>
+      </c>
+      <c r="W47" s="3">
         <v>19500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>21200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>19400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>19900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>3400</v>
       </c>
-      <c r="AA47" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="AB47" s="3" t="s">
         <v>12</v>
       </c>
@@ -3997,83 +4102,86 @@
       <c r="AF47" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>26000</v>
+      </c>
+      <c r="E48" s="3">
         <v>27000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>28800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>30700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>32400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>33500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>39200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>42300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>47000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>50000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>54000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>57100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>52600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>44100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>42900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>43500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>43600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>40200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>27200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>26600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>26100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>21800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>19800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>18900</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="AB48" s="3" t="s">
         <v>12</v>
       </c>
@@ -4089,83 +4197,86 @@
       <c r="AF48" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>367100</v>
+      </c>
+      <c r="E49" s="3">
         <v>375900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>384900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>394400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>403200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>412200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>422300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>432000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>478100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>489800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>500800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>512700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>523500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>647300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1071000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>809700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>829300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>842800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>301700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>310000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>324600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>241500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>246500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>252700</v>
       </c>
-      <c r="AA49" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="AB49" s="3" t="s">
         <v>12</v>
       </c>
@@ -4181,8 +4292,11 @@
       <c r="AF49" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4273,8 +4387,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4365,8 +4482,11 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4406,32 +4526,32 @@
       <c r="O52" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="P52" s="3">
+      <c r="P52" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q52" s="3">
         <v>406000</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
-      </c>
       <c r="R52" s="3">
         <v>0</v>
       </c>
       <c r="S52" s="3">
+        <v>0</v>
+      </c>
+      <c r="T52" s="3">
         <v>50000</v>
-      </c>
-      <c r="T52" s="3">
-        <v>50500</v>
       </c>
       <c r="U52" s="3">
         <v>50500</v>
       </c>
       <c r="V52" s="3">
-        <v>500</v>
+        <v>50500</v>
       </c>
       <c r="W52" s="3">
         <v>500</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>12</v>
+      <c r="X52" s="3">
+        <v>500</v>
       </c>
       <c r="Y52" s="3" t="s">
         <v>12</v>
@@ -4448,8 +4568,8 @@
       <c r="AC52" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="AD52" s="3">
-        <v>0</v>
+      <c r="AD52" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="AE52" s="3">
         <v>0</v>
@@ -4457,8 +4577,11 @@
       <c r="AF52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4549,83 +4672,86 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>650500</v>
+      </c>
+      <c r="E54" s="3">
         <v>683600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>701600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>706800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>691400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>728000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>769500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>792200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>794200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>810900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>811100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>837000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>887400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1372600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1398000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1208800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1197100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1225900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>654800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>646600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>643100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>494500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>479300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>509400</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="AB54" s="3" t="s">
         <v>12</v>
       </c>
@@ -4641,8 +4767,11 @@
       <c r="AF54" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4675,8 +4804,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4709,83 +4839,84 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>24100</v>
+      </c>
+      <c r="E57" s="3">
         <v>10900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>26600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>24200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>19200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>23700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>16800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>24400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>19100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>23000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>17600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>41400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>32800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>36700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>19100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>25700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>22500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>16900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>10900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>9900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>10300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>4400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>8800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>13600</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="AB57" s="3" t="s">
         <v>12</v>
       </c>
@@ -4801,64 +4932,67 @@
       <c r="AF57" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>22900</v>
+      </c>
+      <c r="E58" s="3">
         <v>19200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>15700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>47800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>41700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>31300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>42500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>42400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>40600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>32700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>24300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>15300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>45600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>33100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>31300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>22500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>20300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>18000</v>
-      </c>
-      <c r="U58" s="3">
-        <v>15000</v>
       </c>
       <c r="V58" s="3">
         <v>15000</v>
@@ -4870,14 +5004,14 @@
         <v>15000</v>
       </c>
       <c r="Y58" s="3">
+        <v>15000</v>
+      </c>
+      <c r="Z58" s="3">
         <v>16300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>15000</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="AB58" s="3" t="s">
         <v>12</v>
       </c>
@@ -4893,83 +5027,86 @@
       <c r="AF58" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>63700</v>
+      </c>
+      <c r="E59" s="3">
         <v>78600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>76000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>71600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>77900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>89800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>97900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>115600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>68900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>64300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>74300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>74200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>72900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>351900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>238000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>150600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>128700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>145900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>134800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>133300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>123700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>103200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>86700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>68700</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="AB59" s="3" t="s">
         <v>12</v>
       </c>
@@ -4985,83 +5122,86 @@
       <c r="AF59" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>148100</v>
+      </c>
+      <c r="E60" s="3">
         <v>160400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>161800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>185700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>174800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>210400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>211500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>231500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>173300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>175500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>160800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>179100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>196100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>304000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>288400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>198900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>171500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>180900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>160700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>158200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>149000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>122600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>111700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>97200</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="AB60" s="3" t="s">
         <v>12</v>
       </c>
@@ -5077,83 +5217,86 @@
       <c r="AF60" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>265500</v>
+      </c>
+      <c r="E61" s="3">
         <v>292100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>325500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>312900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>324400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>324800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>362600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>363200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>375300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>388000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>397100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>387100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>424300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>385000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>393100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>351400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>348000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>339600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>162400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>166100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>169700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>173400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>177000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>229700</v>
       </c>
-      <c r="AA61" s="3">
-        <v>0</v>
-      </c>
       <c r="AB61" s="3">
         <v>0</v>
       </c>
@@ -5169,83 +5312,86 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E62" s="3">
         <v>2200</v>
-      </c>
-      <c r="E62" s="3">
-        <v>6300</v>
       </c>
       <c r="F62" s="3">
         <v>6300</v>
       </c>
       <c r="G62" s="3">
+        <v>6300</v>
+      </c>
+      <c r="H62" s="3">
         <v>6100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>6600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>8600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>8500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>26900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>25100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>26700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>37500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>26300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>350700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>337400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>138300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>155700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>171600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>101200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>103000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>104000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>54300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>45200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>40700</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="AB62" s="3" t="s">
         <v>12</v>
       </c>
@@ -5261,8 +5407,11 @@
       <c r="AF62" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5353,8 +5502,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5445,8 +5597,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5537,83 +5692,86 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>416300</v>
+      </c>
+      <c r="E66" s="3">
         <v>455100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>494300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>505500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>505900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>542400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>582700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>603100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>576800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>589800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>584600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>603600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>647000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1047400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1054600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>760800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>747400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>766900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>502300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>505100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>500700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>352200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>336100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>370200</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="AB66" s="3" t="s">
         <v>12</v>
       </c>
@@ -5629,8 +5787,11 @@
       <c r="AF66" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5663,8 +5824,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5755,8 +5917,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5847,8 +6012,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5913,7 +6081,7 @@
         <v>0</v>
       </c>
       <c r="X70" s="3">
-        <v>168000</v>
+        <v>0</v>
       </c>
       <c r="Y70" s="3">
         <v>168000</v>
@@ -5922,7 +6090,7 @@
         <v>168000</v>
       </c>
       <c r="AA70" s="3">
-        <v>0</v>
+        <v>168000</v>
       </c>
       <c r="AB70" s="3">
         <v>0</v>
@@ -5939,8 +6107,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6031,83 +6202,86 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-331800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-334900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-349700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-352800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-360300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-357700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-354900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-350100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-326100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-321500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-315400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-308100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-304500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-165300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-133400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-25100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-17900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-6600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-6200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-5200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-1000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-140700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-138400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-141500</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="AB72" s="3" t="s">
         <v>12</v>
       </c>
@@ -6123,8 +6297,11 @@
       <c r="AF72" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6215,8 +6392,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6307,8 +6487,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6399,83 +6582,86 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>188900</v>
+      </c>
+      <c r="E76" s="3">
         <v>184100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>166100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>161200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>148100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>147900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>148700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>150900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>171300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>173600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>177500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>183200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>188500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>325200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>343400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>448000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>449800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>458900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>152500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>141600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>142400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-25800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-24800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-28800</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="AB76" s="3" t="s">
         <v>12</v>
       </c>
@@ -6491,8 +6677,11 @@
       <c r="AF76" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6583,197 +6772,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46109</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45927</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45836</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45745</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45563</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45472</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45381</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45108</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45017</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44835</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44744</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44653</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44471</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44380</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44289</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44100</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44009</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43918</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43645</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42735</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42462</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42369</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E81" s="3">
         <v>14800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>7500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-2600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-5200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-25700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-4900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-6100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-7300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-3700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-139200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-31900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-108200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-7300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-11300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-4100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>24900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>3000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>10900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>2500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-7400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-23400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-7100</v>
       </c>
-      <c r="AF81" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG81" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6806,100 +7004,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E83" s="3">
         <v>-18000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>12300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>13100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>11800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>-18100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>13800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>14600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>16500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>-8500</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="N83" s="3">
+      <c r="N83" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O83" s="3">
         <v>12400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>12500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>23200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>18800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>12400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>12500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>11700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>8500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>7500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>7200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>6900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>7300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>14500</v>
-      </c>
-      <c r="AA83" s="3">
-        <v>7300</v>
       </c>
       <c r="AB83" s="3">
         <v>7300</v>
       </c>
       <c r="AC83" s="3">
+        <v>7300</v>
+      </c>
+      <c r="AD83" s="3">
         <v>15700</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="AE83" s="3">
+      <c r="AE83" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF83" s="3">
         <v>9100</v>
       </c>
-      <c r="AF83" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6990,8 +7192,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7082,8 +7287,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7174,8 +7382,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7266,8 +7477,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7358,100 +7572,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E89" s="3">
         <v>38000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>30100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>25900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-19300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>19300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>10300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>15200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-6000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>10400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-8300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>10800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>5200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-21000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>13100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>10600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>17300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-18000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>25400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>20800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>25500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>17700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>21000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>8000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>37100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>2200</v>
       </c>
-      <c r="AF89" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7484,8 +7704,9 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7493,91 +7714,94 @@
         <v>-600</v>
       </c>
       <c r="E91" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F91" s="3">
         <v>-500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-600</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-100</v>
       </c>
       <c r="J91" s="3">
         <v>-100</v>
       </c>
       <c r="K91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L91" s="3">
         <v>-300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-3000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1300</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="AE91" s="3">
+      <c r="AE91" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-600</v>
       </c>
-      <c r="AF91" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7668,8 +7892,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7760,8 +7987,11 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7769,91 +7999,94 @@
         <v>-600</v>
       </c>
       <c r="E94" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F94" s="3">
         <v>-500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>24100</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-100</v>
       </c>
       <c r="J94" s="3">
         <v>-100</v>
       </c>
       <c r="K94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L94" s="3">
         <v>-1000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>33500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-15100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-56300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-52000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-4700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-221300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-13200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-46600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-17800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-7300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-7900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-6600</v>
       </c>
-      <c r="AF94" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7886,8 +8119,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7927,8 +8161,8 @@
       <c r="O96" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -7978,8 +8212,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8070,8 +8307,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8162,8 +8402,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8254,280 +8497,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-23100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-28400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-20000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-14700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-42900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-7800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-4200</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>8200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-62200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>27400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>50700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>7700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>9200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>176300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-4300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-6100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>107500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-9900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-57100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>37400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>48800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-11100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-9000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>5500</v>
       </c>
-      <c r="AF100" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>400</v>
+      </c>
+      <c r="E101" s="3">
         <v>-2100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1100</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="N101" s="3">
+      <c r="N101" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O101" s="3">
         <v>-200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1100</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>-200</v>
       </c>
       <c r="R101" s="3">
         <v>-200</v>
       </c>
       <c r="S101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="T101" s="3">
         <v>-100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>500</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-200</v>
-      </c>
-      <c r="AA101" s="3">
-        <v>-300</v>
       </c>
       <c r="AB101" s="3">
         <v>-300</v>
       </c>
       <c r="AC101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AD101" s="3">
         <v>300</v>
       </c>
-      <c r="AD101" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="AE101" s="3">
+      <c r="AE101" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF101" s="3">
         <v>200</v>
       </c>
-      <c r="AF101" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="E102" s="3">
         <v>9100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>9300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>10100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-18800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>11100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>6800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-11800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>10100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-17700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>15300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-6600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-41700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-16600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-31700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-7200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>8600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>42600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>14400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-53800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>61700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>65800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>20900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-10200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>8000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1200</v>
       </c>
-      <c r="AF102" s="3" t="s">
+      <c r="AG102" s="3" t="s">
         <v>12</v>
       </c>
     </row>
